--- a/reports/reports.xlsx
+++ b/reports/reports.xlsx
@@ -21,7 +21,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <name val="Calibri"/>
@@ -120,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -155,6 +157,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -25727,7 +25735,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:KE5"/>
+  <dimension ref="A1:KM5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -25768,259 +25776,267 @@
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="36" max="36"/>
     <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="37" max="37"/>
     <col collapsed="1" width="13" customWidth="1" min="38" max="38"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="39" max="39"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="40" max="40"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="41" max="41"/>
+    <col width="12" customWidth="1" min="39" max="39"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="40" max="40"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="41" max="41"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="42" max="42"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="43" max="43"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="44" max="44"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="45" max="45"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="46" max="46"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="47" max="47"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="48" max="48"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="49" max="49"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="48" max="48"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="49" max="49"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="50" max="50"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="51" max="51"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="52" max="52"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="53" max="53"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="54" max="54"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="55" max="55"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="56" max="56"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="57" max="57"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="56" max="56"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="57" max="57"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="58" max="58"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="59" max="59"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="60" max="60"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="61" max="61"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="62" max="62"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="63" max="63"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="64" max="64"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="65" max="65"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="64" max="64"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="65" max="65"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="66" max="66"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="67" max="67"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="68" max="68"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="69" max="69"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="70" max="70"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="71" max="71"/>
-    <col collapsed="1" width="13" customWidth="1" min="72" max="72"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="73" max="73"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="74" max="74"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="71" max="71"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="72" max="72"/>
+    <col collapsed="1" width="13" customWidth="1" min="73" max="73"/>
+    <col width="12" customWidth="1" min="74" max="74"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="75" max="75"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="76" max="76"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="76" max="76"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="77" max="77"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="78" max="78"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="79" max="79"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="80" max="80"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="81" max="81"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="82" max="82"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="82" max="82"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="83" max="83"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="84" max="84"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="84" max="84"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="85" max="85"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="86" max="86"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="87" max="87"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="88" max="88"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="89" max="89"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="90" max="90"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="90" max="90"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="91" max="91"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="92" max="92"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="92" max="92"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="93" max="93"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="94" max="94"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="95" max="95"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="96" max="96"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="97" max="97"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="98" max="98"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="98" max="98"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="99" max="99"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="100" max="100"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="100" max="100"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="101" max="101"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="102" max="102"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="103" max="103"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="104" max="104"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="105" max="105"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="106" max="106"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="106" max="106"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="107" max="107"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="108" max="108"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="109" max="109"/>
-    <col collapsed="1" width="13" customWidth="1" min="110" max="110"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="111" max="111"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="112" max="112"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="113" max="113"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="108" max="108"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="109" max="109"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="110" max="110"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="111" max="111"/>
+    <col collapsed="1" width="13" customWidth="1" min="112" max="112"/>
+    <col width="12" customWidth="1" min="113" max="113"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="114" max="114"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="115" max="115"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="116" max="116"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="116" max="116"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="117" max="117"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="118" max="118"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="119" max="119"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="119" max="119"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="120" max="120"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="121" max="121"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="122" max="122"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="123" max="123"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="124" max="124"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="124" max="124"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="125" max="125"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="126" max="126"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="127" max="127"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="127" max="127"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="128" max="128"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="129" max="129"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="130" max="130"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="131" max="131"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="132" max="132"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="132" max="132"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="133" max="133"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="134" max="134"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="135" max="135"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="135" max="135"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="136" max="136"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="137" max="137"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="138" max="138"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="139" max="139"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="140" max="140"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="140" max="140"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="141" max="141"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="142" max="142"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="143" max="143"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="143" max="143"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="144" max="144"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="145" max="145"/>
-    <col collapsed="1" width="13" customWidth="1" min="146" max="146"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="145" max="145"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="146" max="146"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="147" max="147"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="148" max="148"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="149" max="149"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="150" max="150"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="148" max="148"/>
+    <col collapsed="1" width="13" customWidth="1" min="149" max="149"/>
+    <col width="12" customWidth="1" min="150" max="150"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="151" max="151"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="152" max="152"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="153" max="153"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="154" max="154"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="154" max="154"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="155" max="155"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="156" max="156"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="157" max="157"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="158" max="158"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="158" max="158"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="159" max="159"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="160" max="160"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="161" max="161"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="162" max="162"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="162" max="162"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="163" max="163"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="164" max="164"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="165" max="165"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="166" max="166"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="166" max="166"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="167" max="167"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="168" max="168"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="169" max="169"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="170" max="170"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="170" max="170"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="171" max="171"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="172" max="172"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="173" max="173"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="174" max="174"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="174" max="174"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="175" max="175"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="176" max="176"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="177" max="177"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="178" max="178"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="178" max="178"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="179" max="179"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="180" max="180"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="181" max="181"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="182" max="182"/>
-    <col collapsed="1" width="13" customWidth="1" min="183" max="183"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="182" max="182"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="183" max="183"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="184" max="184"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="185" max="185"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="186" max="186"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="187" max="187"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="188" max="188"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="186" max="186"/>
+    <col collapsed="1" width="13" customWidth="1" min="187" max="187"/>
+    <col width="12" customWidth="1" min="188" max="188"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="189" max="189"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="190" max="190"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="191" max="191"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="191" max="191"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="192" max="192"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="193" max="193"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="194" max="194"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="195" max="195"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="196" max="196"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="196" max="196"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="197" max="197"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="198" max="198"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="199" max="199"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="199" max="199"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="200" max="200"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="201" max="201"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="202" max="202"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="203" max="203"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="204" max="204"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="204" max="204"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="205" max="205"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="206" max="206"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="207" max="207"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="207" max="207"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="208" max="208"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="209" max="209"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="210" max="210"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="211" max="211"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="212" max="212"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="212" max="212"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="213" max="213"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="214" max="214"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="215" max="215"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="215" max="215"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="216" max="216"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="217" max="217"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="218" max="218"/>
-    <col collapsed="1" width="13" customWidth="1" min="219" max="219"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="220" max="220"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="218" max="218"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="219" max="219"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="220" max="220"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="221" max="221"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="222" max="222"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="223" max="223"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="224" max="224"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="225" max="225"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="223" max="223"/>
+    <col collapsed="1" width="13" customWidth="1" min="224" max="224"/>
+    <col width="12" customWidth="1" min="225" max="225"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="226" max="226"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="227" max="227"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="228" max="228"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="229" max="229"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="230" max="230"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="231" max="231"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="231" max="231"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="232" max="232"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="233" max="233"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="233" max="233"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="234" max="234"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="235" max="235"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="236" max="236"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="237" max="237"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="238" max="238"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="239" max="239"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="239" max="239"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="240" max="240"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="241" max="241"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="241" max="241"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="242" max="242"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="243" max="243"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="244" max="244"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="245" max="245"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="246" max="246"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="247" max="247"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="247" max="247"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="248" max="248"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="249" max="249"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="249" max="249"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="250" max="250"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="251" max="251"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="252" max="252"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="253" max="253"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="254" max="254"/>
     <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="255" max="255"/>
-    <col collapsed="1" width="13" customWidth="1" min="256" max="256"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="256" max="256"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="257" max="257"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="258" max="258"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="259" max="259"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="259" max="259"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="260" max="260"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="261" max="261"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="262" max="262"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="263" max="263"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="261" max="261"/>
+    <col collapsed="1" width="13" customWidth="1" min="262" max="262"/>
+    <col width="12" customWidth="1" min="263" max="263"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="264" max="264"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="265" max="265"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="266" max="266"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="267" max="267"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="266" max="266"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="267" max="267"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="268" max="268"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="269" max="269"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="270" max="270"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="271" max="271"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="272" max="272"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="273" max="273"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="274" max="274"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="275" max="275"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="274" max="274"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="275" max="275"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="276" max="276"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="277" max="277"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="278" max="278"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="279" max="279"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="280" max="280"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="281" max="281"/>
-    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="282" max="282"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="283" max="283"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="282" max="282"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="283" max="283"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="284" max="284"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="285" max="285"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="286" max="286"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="287" max="287"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="288" max="288"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="289" max="289"/>
-    <col collapsed="1" width="13" customWidth="1" min="290" max="290"/>
-    <col width="14" customWidth="1" min="291" max="291"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="289" max="289"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="290" max="290"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="291" max="291"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="292" max="292"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="293" max="293"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="294" max="294"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="295" max="295"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="296" max="296"/>
+    <col collapsed="1" width="13" customWidth="1" min="297" max="297"/>
+    <col width="12" customWidth="1" min="298" max="298"/>
+    <col width="14" customWidth="1" min="299" max="299"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26323,6 +26339,14 @@
       <c r="KC1" s="14" t="n"/>
       <c r="KD1" s="14" t="n"/>
       <c r="KE1" s="14" t="n"/>
+      <c r="KF1" s="14" t="n"/>
+      <c r="KG1" s="14" t="n"/>
+      <c r="KH1" s="14" t="n"/>
+      <c r="KI1" s="14" t="n"/>
+      <c r="KJ1" s="14" t="n"/>
+      <c r="KK1" s="14" t="n"/>
+      <c r="KL1" s="14" t="n"/>
+      <c r="KM1" s="14" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n"/>
@@ -26513,1265 +26537,1305 @@
       </c>
       <c r="AM2" s="14" t="inlineStr">
         <is>
+          <t>% of Target</t>
+        </is>
+      </c>
+      <c r="AN2" s="14" t="inlineStr">
+        <is>
           <t>2026-02-01</t>
         </is>
       </c>
-      <c r="AN2" s="14" t="inlineStr">
+      <c r="AO2" s="14" t="inlineStr">
         <is>
           <t>W1 Feb</t>
         </is>
       </c>
-      <c r="AO2" s="14" t="inlineStr">
+      <c r="AP2" s="14" t="inlineStr">
         <is>
           <t>2026-02-02</t>
         </is>
       </c>
-      <c r="AP2" s="14" t="inlineStr">
+      <c r="AQ2" s="14" t="inlineStr">
         <is>
           <t>2026-02-03</t>
         </is>
       </c>
-      <c r="AQ2" s="14" t="inlineStr">
+      <c r="AR2" s="14" t="inlineStr">
         <is>
           <t>2026-02-04</t>
         </is>
       </c>
-      <c r="AR2" s="14" t="inlineStr">
+      <c r="AS2" s="14" t="inlineStr">
         <is>
           <t>2026-02-05</t>
         </is>
       </c>
-      <c r="AS2" s="14" t="inlineStr">
+      <c r="AT2" s="14" t="inlineStr">
         <is>
           <t>2026-02-06</t>
         </is>
       </c>
-      <c r="AT2" s="14" t="inlineStr">
+      <c r="AU2" s="14" t="inlineStr">
         <is>
           <t>2026-02-07</t>
         </is>
       </c>
-      <c r="AU2" s="14" t="inlineStr">
+      <c r="AV2" s="14" t="inlineStr">
         <is>
           <t>2026-02-08</t>
         </is>
       </c>
-      <c r="AV2" s="14" t="inlineStr">
+      <c r="AW2" s="14" t="inlineStr">
         <is>
           <t>W2 Feb</t>
         </is>
       </c>
-      <c r="AW2" s="14" t="inlineStr">
+      <c r="AX2" s="14" t="inlineStr">
         <is>
           <t>2026-02-09</t>
         </is>
       </c>
-      <c r="AX2" s="14" t="inlineStr">
+      <c r="AY2" s="14" t="inlineStr">
         <is>
           <t>2026-02-10</t>
         </is>
       </c>
-      <c r="AY2" s="14" t="inlineStr">
+      <c r="AZ2" s="14" t="inlineStr">
         <is>
           <t>2026-02-11</t>
         </is>
       </c>
-      <c r="AZ2" s="14" t="inlineStr">
+      <c r="BA2" s="14" t="inlineStr">
         <is>
           <t>2026-02-12</t>
         </is>
       </c>
-      <c r="BA2" s="14" t="inlineStr">
+      <c r="BB2" s="14" t="inlineStr">
         <is>
           <t>2026-02-13</t>
         </is>
       </c>
-      <c r="BB2" s="14" t="inlineStr">
+      <c r="BC2" s="14" t="inlineStr">
         <is>
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="BC2" s="14" t="inlineStr">
+      <c r="BD2" s="14" t="inlineStr">
         <is>
           <t>2026-02-15</t>
         </is>
       </c>
-      <c r="BD2" s="14" t="inlineStr">
+      <c r="BE2" s="14" t="inlineStr">
         <is>
           <t>W3 Feb</t>
         </is>
       </c>
-      <c r="BE2" s="14" t="inlineStr">
+      <c r="BF2" s="14" t="inlineStr">
         <is>
           <t>2026-02-16</t>
         </is>
       </c>
-      <c r="BF2" s="14" t="inlineStr">
+      <c r="BG2" s="14" t="inlineStr">
         <is>
           <t>2026-02-17</t>
         </is>
       </c>
-      <c r="BG2" s="14" t="inlineStr">
+      <c r="BH2" s="14" t="inlineStr">
         <is>
           <t>2026-02-18</t>
         </is>
       </c>
-      <c r="BH2" s="14" t="inlineStr">
+      <c r="BI2" s="14" t="inlineStr">
         <is>
           <t>2026-02-19</t>
         </is>
       </c>
-      <c r="BI2" s="14" t="inlineStr">
+      <c r="BJ2" s="14" t="inlineStr">
         <is>
           <t>2026-02-20</t>
         </is>
       </c>
-      <c r="BJ2" s="14" t="inlineStr">
+      <c r="BK2" s="14" t="inlineStr">
         <is>
           <t>2026-02-21</t>
         </is>
       </c>
-      <c r="BK2" s="14" t="inlineStr">
+      <c r="BL2" s="14" t="inlineStr">
         <is>
           <t>2026-02-22</t>
         </is>
       </c>
-      <c r="BL2" s="14" t="inlineStr">
+      <c r="BM2" s="14" t="inlineStr">
         <is>
           <t>W4 Feb</t>
         </is>
       </c>
-      <c r="BM2" s="14" t="inlineStr">
+      <c r="BN2" s="14" t="inlineStr">
         <is>
           <t>2026-02-23</t>
         </is>
       </c>
-      <c r="BN2" s="14" t="inlineStr">
+      <c r="BO2" s="14" t="inlineStr">
         <is>
           <t>2026-02-24</t>
         </is>
       </c>
-      <c r="BO2" s="14" t="inlineStr">
+      <c r="BP2" s="14" t="inlineStr">
         <is>
           <t>2026-02-25</t>
         </is>
       </c>
-      <c r="BP2" s="14" t="inlineStr">
+      <c r="BQ2" s="14" t="inlineStr">
         <is>
           <t>2026-02-26</t>
         </is>
       </c>
-      <c r="BQ2" s="14" t="inlineStr">
+      <c r="BR2" s="14" t="inlineStr">
         <is>
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="BR2" s="14" t="inlineStr">
+      <c r="BS2" s="14" t="inlineStr">
         <is>
           <t>2026-02-28</t>
         </is>
       </c>
-      <c r="BS2" s="14" t="inlineStr">
+      <c r="BT2" s="14" t="inlineStr">
         <is>
           <t>W5 Feb</t>
         </is>
       </c>
-      <c r="BT2" s="14" t="inlineStr">
+      <c r="BU2" s="14" t="inlineStr">
         <is>
           <t>Feb Total</t>
         </is>
       </c>
-      <c r="BU2" s="14" t="inlineStr">
+      <c r="BV2" s="14" t="inlineStr">
+        <is>
+          <t>% of Target</t>
+        </is>
+      </c>
+      <c r="BW2" s="14" t="inlineStr">
         <is>
           <t>2026-03-01</t>
         </is>
       </c>
-      <c r="BV2" s="14" t="inlineStr">
+      <c r="BX2" s="14" t="inlineStr">
         <is>
           <t>W1 Mar</t>
         </is>
       </c>
-      <c r="BW2" s="14" t="inlineStr">
+      <c r="BY2" s="14" t="inlineStr">
         <is>
           <t>2026-03-02</t>
         </is>
       </c>
-      <c r="BX2" s="14" t="inlineStr">
+      <c r="BZ2" s="14" t="inlineStr">
         <is>
           <t>2026-03-03</t>
         </is>
       </c>
-      <c r="BY2" s="14" t="inlineStr">
+      <c r="CA2" s="14" t="inlineStr">
         <is>
           <t>2026-03-04</t>
         </is>
       </c>
-      <c r="BZ2" s="14" t="inlineStr">
+      <c r="CB2" s="14" t="inlineStr">
         <is>
           <t>2026-03-05</t>
         </is>
       </c>
-      <c r="CA2" s="14" t="inlineStr">
+      <c r="CC2" s="14" t="inlineStr">
         <is>
           <t>2026-03-06</t>
         </is>
       </c>
-      <c r="CB2" s="14" t="inlineStr">
+      <c r="CD2" s="14" t="inlineStr">
         <is>
           <t>2026-03-07</t>
         </is>
       </c>
-      <c r="CC2" s="14" t="inlineStr">
+      <c r="CE2" s="14" t="inlineStr">
         <is>
           <t>2026-03-08</t>
         </is>
       </c>
-      <c r="CD2" s="14" t="inlineStr">
+      <c r="CF2" s="14" t="inlineStr">
         <is>
           <t>W2 Mar</t>
         </is>
       </c>
-      <c r="CE2" s="14" t="inlineStr">
+      <c r="CG2" s="14" t="inlineStr">
         <is>
           <t>2026-03-09</t>
         </is>
       </c>
-      <c r="CF2" s="14" t="inlineStr">
+      <c r="CH2" s="14" t="inlineStr">
         <is>
           <t>2026-03-10</t>
         </is>
       </c>
-      <c r="CG2" s="14" t="inlineStr">
+      <c r="CI2" s="14" t="inlineStr">
         <is>
           <t>2026-03-11</t>
         </is>
       </c>
-      <c r="CH2" s="14" t="inlineStr">
+      <c r="CJ2" s="14" t="inlineStr">
         <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="CI2" s="14" t="inlineStr">
+      <c r="CK2" s="14" t="inlineStr">
         <is>
           <t>2026-03-13</t>
         </is>
       </c>
-      <c r="CJ2" s="14" t="inlineStr">
+      <c r="CL2" s="14" t="inlineStr">
         <is>
           <t>2026-03-14</t>
         </is>
       </c>
-      <c r="CK2" s="14" t="inlineStr">
+      <c r="CM2" s="14" t="inlineStr">
         <is>
           <t>2026-03-15</t>
         </is>
       </c>
-      <c r="CL2" s="14" t="inlineStr">
+      <c r="CN2" s="14" t="inlineStr">
         <is>
           <t>W3 Mar</t>
         </is>
       </c>
-      <c r="CM2" s="14" t="inlineStr">
+      <c r="CO2" s="14" t="inlineStr">
         <is>
           <t>2026-03-16</t>
         </is>
       </c>
-      <c r="CN2" s="14" t="inlineStr">
+      <c r="CP2" s="14" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="CO2" s="14" t="inlineStr">
+      <c r="CQ2" s="14" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="CP2" s="14" t="inlineStr">
+      <c r="CR2" s="14" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="CQ2" s="14" t="inlineStr">
+      <c r="CS2" s="14" t="inlineStr">
         <is>
           <t>2026-03-20</t>
         </is>
       </c>
-      <c r="CR2" s="14" t="inlineStr">
+      <c r="CT2" s="14" t="inlineStr">
         <is>
           <t>2026-03-21</t>
         </is>
       </c>
-      <c r="CS2" s="14" t="inlineStr">
+      <c r="CU2" s="14" t="inlineStr">
         <is>
           <t>2026-03-22</t>
         </is>
       </c>
-      <c r="CT2" s="14" t="inlineStr">
+      <c r="CV2" s="14" t="inlineStr">
         <is>
           <t>W4 Mar</t>
         </is>
       </c>
-      <c r="CU2" s="14" t="inlineStr">
+      <c r="CW2" s="14" t="inlineStr">
         <is>
           <t>2026-03-23</t>
         </is>
       </c>
-      <c r="CV2" s="14" t="inlineStr">
+      <c r="CX2" s="14" t="inlineStr">
         <is>
           <t>2026-03-24</t>
         </is>
       </c>
-      <c r="CW2" s="14" t="inlineStr">
+      <c r="CY2" s="14" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="CX2" s="14" t="inlineStr">
+      <c r="CZ2" s="14" t="inlineStr">
         <is>
           <t>2026-03-26</t>
         </is>
       </c>
-      <c r="CY2" s="14" t="inlineStr">
+      <c r="DA2" s="14" t="inlineStr">
         <is>
           <t>2026-03-27</t>
         </is>
       </c>
-      <c r="CZ2" s="14" t="inlineStr">
+      <c r="DB2" s="14" t="inlineStr">
         <is>
           <t>2026-03-28</t>
         </is>
       </c>
-      <c r="DA2" s="14" t="inlineStr">
+      <c r="DC2" s="14" t="inlineStr">
         <is>
           <t>2026-03-29</t>
         </is>
       </c>
-      <c r="DB2" s="14" t="inlineStr">
+      <c r="DD2" s="14" t="inlineStr">
         <is>
           <t>W5 Mar</t>
         </is>
       </c>
-      <c r="DC2" s="14" t="inlineStr">
+      <c r="DE2" s="14" t="inlineStr">
         <is>
           <t>2026-03-30</t>
         </is>
       </c>
-      <c r="DD2" s="14" t="inlineStr">
+      <c r="DF2" s="14" t="inlineStr">
         <is>
           <t>2026-03-31</t>
         </is>
       </c>
-      <c r="DE2" s="14" t="inlineStr">
+      <c r="DG2" s="14" t="inlineStr">
         <is>
           <t>W6 Mar</t>
         </is>
       </c>
-      <c r="DF2" s="14" t="inlineStr">
+      <c r="DH2" s="14" t="inlineStr">
         <is>
           <t>Mar Total</t>
         </is>
       </c>
-      <c r="DG2" s="14" t="inlineStr">
+      <c r="DI2" s="14" t="inlineStr">
+        <is>
+          <t>% of Target</t>
+        </is>
+      </c>
+      <c r="DJ2" s="14" t="inlineStr">
         <is>
           <t>2026-04-01</t>
         </is>
       </c>
-      <c r="DH2" s="14" t="inlineStr">
+      <c r="DK2" s="14" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="DI2" s="14" t="inlineStr">
+      <c r="DL2" s="14" t="inlineStr">
         <is>
           <t>2026-04-03</t>
         </is>
       </c>
-      <c r="DJ2" s="14" t="inlineStr">
+      <c r="DM2" s="14" t="inlineStr">
         <is>
           <t>2026-04-04</t>
         </is>
       </c>
-      <c r="DK2" s="14" t="inlineStr">
+      <c r="DN2" s="14" t="inlineStr">
         <is>
           <t>2026-04-05</t>
         </is>
       </c>
-      <c r="DL2" s="14" t="inlineStr">
+      <c r="DO2" s="14" t="inlineStr">
         <is>
           <t>W1 Apr</t>
         </is>
       </c>
-      <c r="DM2" s="14" t="inlineStr">
+      <c r="DP2" s="14" t="inlineStr">
         <is>
           <t>2026-04-06</t>
         </is>
       </c>
-      <c r="DN2" s="14" t="inlineStr">
+      <c r="DQ2" s="14" t="inlineStr">
         <is>
           <t>2026-04-07</t>
         </is>
       </c>
-      <c r="DO2" s="14" t="inlineStr">
+      <c r="DR2" s="14" t="inlineStr">
         <is>
           <t>2026-04-08</t>
         </is>
       </c>
-      <c r="DP2" s="14" t="inlineStr">
+      <c r="DS2" s="14" t="inlineStr">
         <is>
           <t>2026-04-09</t>
         </is>
       </c>
-      <c r="DQ2" s="14" t="inlineStr">
+      <c r="DT2" s="14" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="DR2" s="14" t="inlineStr">
+      <c r="DU2" s="14" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="DS2" s="14" t="inlineStr">
+      <c r="DV2" s="14" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="DT2" s="14" t="inlineStr">
+      <c r="DW2" s="14" t="inlineStr">
         <is>
           <t>W2 Apr</t>
         </is>
       </c>
-      <c r="DU2" s="14" t="inlineStr">
+      <c r="DX2" s="14" t="inlineStr">
         <is>
           <t>2026-04-13</t>
         </is>
       </c>
-      <c r="DV2" s="14" t="inlineStr">
+      <c r="DY2" s="14" t="inlineStr">
         <is>
           <t>2026-04-14</t>
         </is>
       </c>
-      <c r="DW2" s="14" t="inlineStr">
+      <c r="DZ2" s="14" t="inlineStr">
         <is>
           <t>2026-04-15</t>
         </is>
       </c>
-      <c r="DX2" s="14" t="inlineStr">
+      <c r="EA2" s="14" t="inlineStr">
         <is>
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="DY2" s="14" t="inlineStr">
+      <c r="EB2" s="14" t="inlineStr">
         <is>
           <t>2026-04-17</t>
         </is>
       </c>
-      <c r="DZ2" s="14" t="inlineStr">
+      <c r="EC2" s="14" t="inlineStr">
         <is>
           <t>2026-04-18</t>
         </is>
       </c>
-      <c r="EA2" s="14" t="inlineStr">
+      <c r="ED2" s="14" t="inlineStr">
         <is>
           <t>2026-04-19</t>
         </is>
       </c>
-      <c r="EB2" s="14" t="inlineStr">
+      <c r="EE2" s="14" t="inlineStr">
         <is>
           <t>W3 Apr</t>
         </is>
       </c>
-      <c r="EC2" s="14" t="inlineStr">
+      <c r="EF2" s="14" t="inlineStr">
         <is>
           <t>2026-04-20</t>
         </is>
       </c>
-      <c r="ED2" s="14" t="inlineStr">
+      <c r="EG2" s="14" t="inlineStr">
         <is>
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="EE2" s="14" t="inlineStr">
+      <c r="EH2" s="14" t="inlineStr">
         <is>
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="EF2" s="14" t="inlineStr">
+      <c r="EI2" s="14" t="inlineStr">
         <is>
           <t>2026-04-23</t>
         </is>
       </c>
-      <c r="EG2" s="14" t="inlineStr">
+      <c r="EJ2" s="14" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="EH2" s="14" t="inlineStr">
+      <c r="EK2" s="14" t="inlineStr">
         <is>
           <t>2026-04-25</t>
         </is>
       </c>
-      <c r="EI2" s="14" t="inlineStr">
+      <c r="EL2" s="14" t="inlineStr">
         <is>
           <t>2026-04-26</t>
         </is>
       </c>
-      <c r="EJ2" s="14" t="inlineStr">
+      <c r="EM2" s="14" t="inlineStr">
         <is>
           <t>W4 Apr</t>
         </is>
       </c>
-      <c r="EK2" s="14" t="inlineStr">
+      <c r="EN2" s="14" t="inlineStr">
         <is>
           <t>2026-04-27</t>
         </is>
       </c>
-      <c r="EL2" s="14" t="inlineStr">
+      <c r="EO2" s="14" t="inlineStr">
         <is>
           <t>2026-04-28</t>
         </is>
       </c>
-      <c r="EM2" s="14" t="inlineStr">
+      <c r="EP2" s="14" t="inlineStr">
         <is>
           <t>2026-04-29</t>
         </is>
       </c>
-      <c r="EN2" s="14" t="inlineStr">
+      <c r="EQ2" s="14" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
       </c>
-      <c r="EO2" s="14" t="inlineStr">
+      <c r="ER2" s="14" t="inlineStr">
         <is>
           <t>W5 Apr</t>
         </is>
       </c>
-      <c r="EP2" s="14" t="inlineStr">
+      <c r="ES2" s="14" t="inlineStr">
         <is>
           <t>Apr Total</t>
         </is>
       </c>
-      <c r="EQ2" s="14" t="inlineStr">
+      <c r="ET2" s="14" t="inlineStr">
+        <is>
+          <t>% of Target</t>
+        </is>
+      </c>
+      <c r="EU2" s="14" t="inlineStr">
         <is>
           <t>2026-05-01</t>
         </is>
       </c>
-      <c r="ER2" s="14" t="inlineStr">
+      <c r="EV2" s="14" t="inlineStr">
         <is>
           <t>2026-05-02</t>
         </is>
       </c>
-      <c r="ES2" s="14" t="inlineStr">
+      <c r="EW2" s="14" t="inlineStr">
         <is>
           <t>2026-05-03</t>
         </is>
       </c>
-      <c r="ET2" s="14" t="inlineStr">
+      <c r="EX2" s="14" t="inlineStr">
         <is>
           <t>W1 May</t>
         </is>
       </c>
-      <c r="EU2" s="14" t="inlineStr">
+      <c r="EY2" s="14" t="inlineStr">
         <is>
           <t>2026-05-04</t>
         </is>
       </c>
-      <c r="EV2" s="14" t="inlineStr">
+      <c r="EZ2" s="14" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="EW2" s="14" t="inlineStr">
+      <c r="FA2" s="14" t="inlineStr">
         <is>
           <t>2026-05-06</t>
         </is>
       </c>
-      <c r="EX2" s="14" t="inlineStr">
+      <c r="FB2" s="14" t="inlineStr">
         <is>
           <t>2026-05-07</t>
         </is>
       </c>
-      <c r="EY2" s="14" t="inlineStr">
+      <c r="FC2" s="14" t="inlineStr">
         <is>
           <t>2026-05-08</t>
         </is>
       </c>
-      <c r="EZ2" s="14" t="inlineStr">
+      <c r="FD2" s="14" t="inlineStr">
         <is>
           <t>2026-05-09</t>
         </is>
       </c>
-      <c r="FA2" s="14" t="inlineStr">
+      <c r="FE2" s="14" t="inlineStr">
         <is>
           <t>2026-05-10</t>
         </is>
       </c>
-      <c r="FB2" s="14" t="inlineStr">
+      <c r="FF2" s="14" t="inlineStr">
         <is>
           <t>W2 May</t>
         </is>
       </c>
-      <c r="FC2" s="14" t="inlineStr">
+      <c r="FG2" s="14" t="inlineStr">
         <is>
           <t>2026-05-11</t>
         </is>
       </c>
-      <c r="FD2" s="14" t="inlineStr">
+      <c r="FH2" s="14" t="inlineStr">
         <is>
           <t>2026-05-12</t>
         </is>
       </c>
-      <c r="FE2" s="14" t="inlineStr">
+      <c r="FI2" s="14" t="inlineStr">
         <is>
           <t>2026-05-13</t>
         </is>
       </c>
-      <c r="FF2" s="14" t="inlineStr">
+      <c r="FJ2" s="14" t="inlineStr">
         <is>
           <t>2026-05-14</t>
         </is>
       </c>
-      <c r="FG2" s="14" t="inlineStr">
+      <c r="FK2" s="14" t="inlineStr">
         <is>
           <t>2026-05-15</t>
         </is>
       </c>
-      <c r="FH2" s="14" t="inlineStr">
+      <c r="FL2" s="14" t="inlineStr">
         <is>
           <t>2026-05-16</t>
         </is>
       </c>
-      <c r="FI2" s="14" t="inlineStr">
+      <c r="FM2" s="14" t="inlineStr">
         <is>
           <t>2026-05-17</t>
         </is>
       </c>
-      <c r="FJ2" s="14" t="inlineStr">
+      <c r="FN2" s="14" t="inlineStr">
         <is>
           <t>W3 May</t>
         </is>
       </c>
-      <c r="FK2" s="14" t="inlineStr">
+      <c r="FO2" s="14" t="inlineStr">
         <is>
           <t>2026-05-18</t>
         </is>
       </c>
-      <c r="FL2" s="14" t="inlineStr">
+      <c r="FP2" s="14" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="FM2" s="14" t="inlineStr">
+      <c r="FQ2" s="14" t="inlineStr">
         <is>
           <t>2026-05-20</t>
         </is>
       </c>
-      <c r="FN2" s="14" t="inlineStr">
+      <c r="FR2" s="14" t="inlineStr">
         <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="FO2" s="14" t="inlineStr">
+      <c r="FS2" s="14" t="inlineStr">
         <is>
           <t>2026-05-22</t>
         </is>
       </c>
-      <c r="FP2" s="14" t="inlineStr">
+      <c r="FT2" s="14" t="inlineStr">
         <is>
           <t>2026-05-23</t>
         </is>
       </c>
-      <c r="FQ2" s="14" t="inlineStr">
+      <c r="FU2" s="14" t="inlineStr">
         <is>
           <t>2026-05-24</t>
         </is>
       </c>
-      <c r="FR2" s="14" t="inlineStr">
+      <c r="FV2" s="14" t="inlineStr">
         <is>
           <t>W4 May</t>
         </is>
       </c>
-      <c r="FS2" s="14" t="inlineStr">
+      <c r="FW2" s="14" t="inlineStr">
         <is>
           <t>2026-05-25</t>
         </is>
       </c>
-      <c r="FT2" s="14" t="inlineStr">
+      <c r="FX2" s="14" t="inlineStr">
         <is>
           <t>2026-05-26</t>
         </is>
       </c>
-      <c r="FU2" s="14" t="inlineStr">
+      <c r="FY2" s="14" t="inlineStr">
         <is>
           <t>2026-05-27</t>
         </is>
       </c>
-      <c r="FV2" s="14" t="inlineStr">
+      <c r="FZ2" s="14" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="FW2" s="14" t="inlineStr">
+      <c r="GA2" s="14" t="inlineStr">
         <is>
           <t>2026-05-29</t>
         </is>
       </c>
-      <c r="FX2" s="14" t="inlineStr">
+      <c r="GB2" s="14" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="FY2" s="14" t="inlineStr">
+      <c r="GC2" s="14" t="inlineStr">
         <is>
           <t>2026-05-31</t>
         </is>
       </c>
-      <c r="FZ2" s="14" t="inlineStr">
+      <c r="GD2" s="14" t="inlineStr">
         <is>
           <t>W5 May</t>
         </is>
       </c>
-      <c r="GA2" s="14" t="inlineStr">
+      <c r="GE2" s="14" t="inlineStr">
         <is>
           <t>May Total</t>
         </is>
       </c>
-      <c r="GB2" s="14" t="inlineStr">
+      <c r="GF2" s="14" t="inlineStr">
+        <is>
+          <t>% of Target</t>
+        </is>
+      </c>
+      <c r="GG2" s="14" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="GC2" s="14" t="inlineStr">
+      <c r="GH2" s="14" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="GD2" s="14" t="inlineStr">
+      <c r="GI2" s="14" t="inlineStr">
         <is>
           <t>2026-06-03</t>
         </is>
       </c>
-      <c r="GE2" s="14" t="inlineStr">
+      <c r="GJ2" s="14" t="inlineStr">
         <is>
           <t>2026-06-04</t>
         </is>
       </c>
-      <c r="GF2" s="14" t="inlineStr">
+      <c r="GK2" s="14" t="inlineStr">
         <is>
           <t>2026-06-05</t>
         </is>
       </c>
-      <c r="GG2" s="14" t="inlineStr">
+      <c r="GL2" s="14" t="inlineStr">
         <is>
           <t>2026-06-06</t>
         </is>
       </c>
-      <c r="GH2" s="14" t="inlineStr">
+      <c r="GM2" s="14" t="inlineStr">
         <is>
           <t>2026-06-07</t>
         </is>
       </c>
-      <c r="GI2" s="14" t="inlineStr">
+      <c r="GN2" s="14" t="inlineStr">
         <is>
           <t>W1 Jun</t>
         </is>
       </c>
-      <c r="GJ2" s="14" t="inlineStr">
+      <c r="GO2" s="14" t="inlineStr">
         <is>
           <t>2026-06-08</t>
         </is>
       </c>
-      <c r="GK2" s="14" t="inlineStr">
+      <c r="GP2" s="14" t="inlineStr">
         <is>
           <t>2026-06-09</t>
         </is>
       </c>
-      <c r="GL2" s="14" t="inlineStr">
+      <c r="GQ2" s="14" t="inlineStr">
         <is>
           <t>2026-06-10</t>
         </is>
       </c>
-      <c r="GM2" s="14" t="inlineStr">
+      <c r="GR2" s="14" t="inlineStr">
         <is>
           <t>2026-06-11</t>
         </is>
       </c>
-      <c r="GN2" s="14" t="inlineStr">
+      <c r="GS2" s="14" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="GO2" s="14" t="inlineStr">
+      <c r="GT2" s="14" t="inlineStr">
         <is>
           <t>2026-06-13</t>
         </is>
       </c>
-      <c r="GP2" s="14" t="inlineStr">
+      <c r="GU2" s="14" t="inlineStr">
         <is>
           <t>2026-06-14</t>
         </is>
       </c>
-      <c r="GQ2" s="14" t="inlineStr">
+      <c r="GV2" s="14" t="inlineStr">
         <is>
           <t>W2 Jun</t>
         </is>
       </c>
-      <c r="GR2" s="14" t="inlineStr">
+      <c r="GW2" s="14" t="inlineStr">
         <is>
           <t>2026-06-15</t>
         </is>
       </c>
-      <c r="GS2" s="14" t="inlineStr">
+      <c r="GX2" s="14" t="inlineStr">
         <is>
           <t>2026-06-16</t>
         </is>
       </c>
-      <c r="GT2" s="14" t="inlineStr">
+      <c r="GY2" s="14" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="GU2" s="14" t="inlineStr">
+      <c r="GZ2" s="14" t="inlineStr">
         <is>
           <t>2026-06-18</t>
         </is>
       </c>
-      <c r="GV2" s="14" t="inlineStr">
+      <c r="HA2" s="14" t="inlineStr">
         <is>
           <t>2026-06-19</t>
         </is>
       </c>
-      <c r="GW2" s="14" t="inlineStr">
+      <c r="HB2" s="14" t="inlineStr">
         <is>
           <t>2026-06-20</t>
         </is>
       </c>
-      <c r="GX2" s="14" t="inlineStr">
+      <c r="HC2" s="14" t="inlineStr">
         <is>
           <t>2026-06-21</t>
         </is>
       </c>
-      <c r="GY2" s="14" t="inlineStr">
+      <c r="HD2" s="14" t="inlineStr">
         <is>
           <t>W3 Jun</t>
         </is>
       </c>
-      <c r="GZ2" s="14" t="inlineStr">
+      <c r="HE2" s="14" t="inlineStr">
         <is>
           <t>2026-06-22</t>
         </is>
       </c>
-      <c r="HA2" s="14" t="inlineStr">
+      <c r="HF2" s="14" t="inlineStr">
         <is>
           <t>2026-06-23</t>
         </is>
       </c>
-      <c r="HB2" s="14" t="inlineStr">
+      <c r="HG2" s="14" t="inlineStr">
         <is>
           <t>2026-06-24</t>
         </is>
       </c>
-      <c r="HC2" s="14" t="inlineStr">
+      <c r="HH2" s="14" t="inlineStr">
         <is>
           <t>2026-06-25</t>
         </is>
       </c>
-      <c r="HD2" s="14" t="inlineStr">
+      <c r="HI2" s="14" t="inlineStr">
         <is>
           <t>2026-06-26</t>
         </is>
       </c>
-      <c r="HE2" s="14" t="inlineStr">
+      <c r="HJ2" s="14" t="inlineStr">
         <is>
           <t>2026-06-27</t>
         </is>
       </c>
-      <c r="HF2" s="14" t="inlineStr">
+      <c r="HK2" s="14" t="inlineStr">
         <is>
           <t>2026-06-28</t>
         </is>
       </c>
-      <c r="HG2" s="14" t="inlineStr">
+      <c r="HL2" s="14" t="inlineStr">
         <is>
           <t>W4 Jun</t>
         </is>
       </c>
-      <c r="HH2" s="14" t="inlineStr">
+      <c r="HM2" s="14" t="inlineStr">
         <is>
           <t>2026-06-29</t>
         </is>
       </c>
-      <c r="HI2" s="14" t="inlineStr">
+      <c r="HN2" s="14" t="inlineStr">
         <is>
           <t>2026-06-30</t>
         </is>
       </c>
-      <c r="HJ2" s="14" t="inlineStr">
+      <c r="HO2" s="14" t="inlineStr">
         <is>
           <t>W5 Jun</t>
         </is>
       </c>
-      <c r="HK2" s="14" t="inlineStr">
+      <c r="HP2" s="14" t="inlineStr">
         <is>
           <t>Jun Total</t>
         </is>
       </c>
-      <c r="HL2" s="14" t="inlineStr">
+      <c r="HQ2" s="14" t="inlineStr">
+        <is>
+          <t>% of Target</t>
+        </is>
+      </c>
+      <c r="HR2" s="14" t="inlineStr">
         <is>
           <t>2026-07-01</t>
         </is>
       </c>
-      <c r="HM2" s="14" t="inlineStr">
+      <c r="HS2" s="14" t="inlineStr">
         <is>
           <t>2026-07-02</t>
         </is>
       </c>
-      <c r="HN2" s="14" t="inlineStr">
+      <c r="HT2" s="14" t="inlineStr">
         <is>
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="HO2" s="14" t="inlineStr">
+      <c r="HU2" s="14" t="inlineStr">
         <is>
           <t>2026-07-04</t>
         </is>
       </c>
-      <c r="HP2" s="14" t="inlineStr">
+      <c r="HV2" s="14" t="inlineStr">
         <is>
           <t>2026-07-05</t>
         </is>
       </c>
-      <c r="HQ2" s="14" t="inlineStr">
+      <c r="HW2" s="14" t="inlineStr">
         <is>
           <t>W1 Jul</t>
         </is>
       </c>
-      <c r="HR2" s="14" t="inlineStr">
+      <c r="HX2" s="14" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="HS2" s="14" t="inlineStr">
+      <c r="HY2" s="14" t="inlineStr">
         <is>
           <t>2026-07-07</t>
         </is>
       </c>
-      <c r="HT2" s="14" t="inlineStr">
+      <c r="HZ2" s="14" t="inlineStr">
         <is>
           <t>2026-07-08</t>
         </is>
       </c>
-      <c r="HU2" s="14" t="inlineStr">
+      <c r="IA2" s="14" t="inlineStr">
         <is>
           <t>2026-07-09</t>
         </is>
       </c>
-      <c r="HV2" s="14" t="inlineStr">
+      <c r="IB2" s="14" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
       </c>
-      <c r="HW2" s="14" t="inlineStr">
+      <c r="IC2" s="14" t="inlineStr">
         <is>
           <t>2026-07-11</t>
         </is>
       </c>
-      <c r="HX2" s="14" t="inlineStr">
+      <c r="ID2" s="14" t="inlineStr">
         <is>
           <t>2026-07-12</t>
         </is>
       </c>
-      <c r="HY2" s="14" t="inlineStr">
+      <c r="IE2" s="14" t="inlineStr">
         <is>
           <t>W2 Jul</t>
         </is>
       </c>
-      <c r="HZ2" s="14" t="inlineStr">
+      <c r="IF2" s="14" t="inlineStr">
         <is>
           <t>2026-07-13</t>
         </is>
       </c>
-      <c r="IA2" s="14" t="inlineStr">
+      <c r="IG2" s="14" t="inlineStr">
         <is>
           <t>2026-07-14</t>
         </is>
       </c>
-      <c r="IB2" s="14" t="inlineStr">
+      <c r="IH2" s="14" t="inlineStr">
         <is>
           <t>2026-07-15</t>
         </is>
       </c>
-      <c r="IC2" s="14" t="inlineStr">
+      <c r="II2" s="14" t="inlineStr">
         <is>
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="ID2" s="14" t="inlineStr">
+      <c r="IJ2" s="14" t="inlineStr">
         <is>
           <t>2026-07-17</t>
         </is>
       </c>
-      <c r="IE2" s="14" t="inlineStr">
+      <c r="IK2" s="14" t="inlineStr">
         <is>
           <t>2026-07-18</t>
         </is>
       </c>
-      <c r="IF2" s="14" t="inlineStr">
+      <c r="IL2" s="14" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="IG2" s="14" t="inlineStr">
+      <c r="IM2" s="14" t="inlineStr">
         <is>
           <t>W3 Jul</t>
         </is>
       </c>
-      <c r="IH2" s="14" t="inlineStr">
+      <c r="IN2" s="14" t="inlineStr">
         <is>
           <t>2026-07-20</t>
         </is>
       </c>
-      <c r="II2" s="14" t="inlineStr">
+      <c r="IO2" s="14" t="inlineStr">
         <is>
           <t>2026-07-21</t>
         </is>
       </c>
-      <c r="IJ2" s="14" t="inlineStr">
+      <c r="IP2" s="14" t="inlineStr">
         <is>
           <t>2026-07-22</t>
         </is>
       </c>
-      <c r="IK2" s="14" t="inlineStr">
+      <c r="IQ2" s="14" t="inlineStr">
         <is>
           <t>2026-07-23</t>
         </is>
       </c>
-      <c r="IL2" s="14" t="inlineStr">
+      <c r="IR2" s="14" t="inlineStr">
         <is>
           <t>2026-07-24</t>
         </is>
       </c>
-      <c r="IM2" s="14" t="inlineStr">
+      <c r="IS2" s="14" t="inlineStr">
         <is>
           <t>2026-07-25</t>
         </is>
       </c>
-      <c r="IN2" s="14" t="inlineStr">
+      <c r="IT2" s="14" t="inlineStr">
         <is>
           <t>2026-07-26</t>
         </is>
       </c>
-      <c r="IO2" s="14" t="inlineStr">
+      <c r="IU2" s="14" t="inlineStr">
         <is>
           <t>W4 Jul</t>
         </is>
       </c>
-      <c r="IP2" s="14" t="inlineStr">
+      <c r="IV2" s="14" t="inlineStr">
         <is>
           <t>2026-07-27</t>
         </is>
       </c>
-      <c r="IQ2" s="14" t="inlineStr">
+      <c r="IW2" s="14" t="inlineStr">
         <is>
           <t>2026-07-28</t>
         </is>
       </c>
-      <c r="IR2" s="14" t="inlineStr">
+      <c r="IX2" s="14" t="inlineStr">
         <is>
           <t>2026-07-29</t>
         </is>
       </c>
-      <c r="IS2" s="14" t="inlineStr">
+      <c r="IY2" s="14" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="IT2" s="14" t="inlineStr">
+      <c r="IZ2" s="14" t="inlineStr">
         <is>
           <t>2026-07-31</t>
         </is>
       </c>
-      <c r="IU2" s="14" t="inlineStr">
+      <c r="JA2" s="14" t="inlineStr">
         <is>
           <t>W5 Jul</t>
         </is>
       </c>
-      <c r="IV2" s="14" t="inlineStr">
+      <c r="JB2" s="14" t="inlineStr">
         <is>
           <t>Jul Total</t>
         </is>
       </c>
-      <c r="IW2" s="14" t="inlineStr">
+      <c r="JC2" s="14" t="inlineStr">
+        <is>
+          <t>% of Target</t>
+        </is>
+      </c>
+      <c r="JD2" s="14" t="inlineStr">
         <is>
           <t>2026-08-01</t>
         </is>
       </c>
-      <c r="IX2" s="14" t="inlineStr">
+      <c r="JE2" s="14" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="IY2" s="14" t="inlineStr">
+      <c r="JF2" s="14" t="inlineStr">
         <is>
           <t>W1 Aug</t>
         </is>
       </c>
-      <c r="IZ2" s="14" t="inlineStr">
+      <c r="JG2" s="14" t="inlineStr">
         <is>
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="JA2" s="14" t="inlineStr">
+      <c r="JH2" s="14" t="inlineStr">
         <is>
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="JB2" s="14" t="inlineStr">
+      <c r="JI2" s="14" t="inlineStr">
         <is>
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="JC2" s="14" t="inlineStr">
+      <c r="JJ2" s="14" t="inlineStr">
         <is>
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="JD2" s="14" t="inlineStr">
+      <c r="JK2" s="14" t="inlineStr">
         <is>
           <t>2026-08-07</t>
         </is>
       </c>
-      <c r="JE2" s="14" t="inlineStr">
+      <c r="JL2" s="14" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="JF2" s="14" t="inlineStr">
+      <c r="JM2" s="14" t="inlineStr">
         <is>
           <t>2026-08-09</t>
         </is>
       </c>
-      <c r="JG2" s="14" t="inlineStr">
+      <c r="JN2" s="14" t="inlineStr">
         <is>
           <t>W2 Aug</t>
         </is>
       </c>
-      <c r="JH2" s="14" t="inlineStr">
+      <c r="JO2" s="14" t="inlineStr">
         <is>
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="JI2" s="14" t="inlineStr">
+      <c r="JP2" s="14" t="inlineStr">
         <is>
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="JJ2" s="14" t="inlineStr">
+      <c r="JQ2" s="14" t="inlineStr">
         <is>
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="JK2" s="14" t="inlineStr">
+      <c r="JR2" s="14" t="inlineStr">
         <is>
           <t>2026-08-13</t>
         </is>
       </c>
-      <c r="JL2" s="14" t="inlineStr">
+      <c r="JS2" s="14" t="inlineStr">
         <is>
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="JM2" s="14" t="inlineStr">
+      <c r="JT2" s="14" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="JN2" s="14" t="inlineStr">
+      <c r="JU2" s="14" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="JO2" s="14" t="inlineStr">
+      <c r="JV2" s="14" t="inlineStr">
         <is>
           <t>W3 Aug</t>
         </is>
       </c>
-      <c r="JP2" s="14" t="inlineStr">
+      <c r="JW2" s="14" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="JQ2" s="14" t="inlineStr">
+      <c r="JX2" s="14" t="inlineStr">
         <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="JR2" s="14" t="inlineStr">
+      <c r="JY2" s="14" t="inlineStr">
         <is>
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="JS2" s="14" t="inlineStr">
+      <c r="JZ2" s="14" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="JT2" s="14" t="inlineStr">
+      <c r="KA2" s="14" t="inlineStr">
         <is>
           <t>2026-08-21</t>
         </is>
       </c>
-      <c r="JU2" s="14" t="inlineStr">
+      <c r="KB2" s="14" t="inlineStr">
         <is>
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="JV2" s="14" t="inlineStr">
+      <c r="KC2" s="14" t="inlineStr">
         <is>
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="JW2" s="14" t="inlineStr">
+      <c r="KD2" s="14" t="inlineStr">
         <is>
           <t>W4 Aug</t>
         </is>
       </c>
-      <c r="JX2" s="14" t="inlineStr">
+      <c r="KE2" s="14" t="inlineStr">
         <is>
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="JY2" s="14" t="inlineStr">
+      <c r="KF2" s="14" t="inlineStr">
         <is>
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="JZ2" s="14" t="inlineStr">
+      <c r="KG2" s="14" t="inlineStr">
         <is>
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="KA2" s="14" t="inlineStr">
+      <c r="KH2" s="14" t="inlineStr">
         <is>
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="KB2" s="14" t="inlineStr">
+      <c r="KI2" s="14" t="inlineStr">
         <is>
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="KC2" s="14" t="inlineStr">
+      <c r="KJ2" s="14" t="inlineStr">
         <is>
           <t>W5 Aug</t>
         </is>
       </c>
-      <c r="KD2" s="14" t="inlineStr">
+      <c r="KK2" s="14" t="inlineStr">
         <is>
           <t>Aug Total</t>
         </is>
       </c>
-      <c r="KE2" s="14" t="inlineStr">
+      <c r="KL2" s="14" t="inlineStr">
+        <is>
+          <t>% of Target</t>
+        </is>
+      </c>
+      <c r="KM2" s="14" t="inlineStr">
         <is>
           <t>YTD Total</t>
         </is>
@@ -27900,14 +27964,15 @@
         <f>SUM(F3,N3,V3,AD3,AK3)</f>
         <v>0</v>
       </c>
-      <c r="AM3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN3" s="5">
-        <f>SUM(AM3:AM3)</f>
-        <v>0</v>
-      </c>
-      <c r="AO3" s="5" t="n">
+      <c r="AM3" s="15">
+        <f>AL3/440</f>
+        <v>0.0</v>
+      </c>
+      <c r="AN3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="5">
+        <f>SUM(AN3:AN3)</f>
         <v>0</v>
       </c>
       <c r="AP3" s="5" t="n">
@@ -27928,11 +27993,11 @@
       <c r="AU3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AV3" s="5">
-        <f>SUM(AO3:AU3)</f>
-        <v>0</v>
-      </c>
-      <c r="AW3" s="5" t="n">
+      <c r="AV3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW3" s="5">
+        <f>SUM(AP3:AV3)</f>
         <v>0</v>
       </c>
       <c r="AX3" s="5" t="n">
@@ -27953,11 +28018,11 @@
       <c r="BC3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="BD3" s="5">
-        <f>SUM(AW3:BC3)</f>
-        <v>0</v>
-      </c>
-      <c r="BE3" s="5" t="n">
+      <c r="BD3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE3" s="5">
+        <f>SUM(AX3:BD3)</f>
         <v>0</v>
       </c>
       <c r="BF3" s="5" t="n">
@@ -27978,11 +28043,11 @@
       <c r="BK3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="BL3" s="5">
-        <f>SUM(BE3:BK3)</f>
-        <v>0</v>
-      </c>
-      <c r="BM3" s="5" t="n">
+      <c r="BL3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM3" s="5">
+        <f>SUM(BF3:BL3)</f>
         <v>0</v>
       </c>
       <c r="BN3" s="5" t="n">
@@ -28000,25 +28065,26 @@
       <c r="BR3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="BS3" s="5">
-        <f>SUM(BM3:BR3)</f>
+      <c r="BS3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="BT3" s="5">
-        <f>SUM(AN3,AV3,BD3,BL3,BS3)</f>
-        <v>0</v>
-      </c>
-      <c r="BU3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV3" s="5">
-        <f>SUM(BU3:BU3)</f>
-        <v>0</v>
+        <f>SUM(BN3:BS3)</f>
+        <v>0</v>
+      </c>
+      <c r="BU3" s="5">
+        <f>SUM(AO3,AW3,BE3,BM3,BT3)</f>
+        <v>0</v>
+      </c>
+      <c r="BV3" s="15">
+        <f>BU3/440</f>
+        <v>0.0</v>
       </c>
       <c r="BW3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="BX3" s="5" t="n">
+      <c r="BX3" s="5">
+        <f>SUM(BW3:BW3)</f>
         <v>0</v>
       </c>
       <c r="BY3" s="5" t="n">
@@ -28036,14 +28102,14 @@
       <c r="CC3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CD3" s="5">
-        <f>SUM(BW3:CC3)</f>
+      <c r="CD3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="CE3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CF3" s="5" t="n">
+      <c r="CF3" s="5">
+        <f>SUM(BY3:CE3)</f>
         <v>0</v>
       </c>
       <c r="CG3" s="5" t="n">
@@ -28061,14 +28127,14 @@
       <c r="CK3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CL3" s="5">
-        <f>SUM(CE3:CK3)</f>
+      <c r="CL3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="CM3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN3" s="5">
+        <f>SUM(CG3:CM3)</f>
         <v>0</v>
       </c>
       <c r="CO3" s="5" t="n">
@@ -28078,7 +28144,7 @@
         <v>0</v>
       </c>
       <c r="CQ3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CR3" s="5" t="n">
         <v>0</v>
@@ -28086,16 +28152,16 @@
       <c r="CS3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CT3" s="5">
-        <f>SUM(CM3:CS3)</f>
+      <c r="CT3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV3" s="5">
+        <f>SUM(CO3:CU3)</f>
         <v>2</v>
       </c>
-      <c r="CU3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV3" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="CW3" s="5" t="n">
         <v>0</v>
       </c>
@@ -28111,76 +28177,77 @@
       <c r="DA3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="DB3" s="5">
-        <f>SUM(CU3:DA3)</f>
+      <c r="DB3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="DC3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="DD3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE3" s="5">
-        <f>SUM(DC3:DD3)</f>
-        <v>0</v>
-      </c>
-      <c r="DF3" s="5">
-        <f>SUM(BV3,CD3,CL3,CT3,DB3,DE3)</f>
+      <c r="DD3" s="5">
+        <f>SUM(CW3:DC3)</f>
+        <v>0</v>
+      </c>
+      <c r="DE3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG3" s="5">
+        <f>SUM(DE3:DF3)</f>
+        <v>0</v>
+      </c>
+      <c r="DH3" s="5">
+        <f>SUM(BX3,CF3,CN3,CV3,DD3,DG3)</f>
         <v>2</v>
       </c>
-      <c r="DG3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="DH3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI3" s="5" t="n">
-        <v>0</v>
+      <c r="DI3" s="15">
+        <f>DH3/440</f>
+        <v>0.004545454545454545</v>
       </c>
       <c r="DJ3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="DL3" s="5">
-        <f>SUM(DG3:DK3)</f>
-        <v>1</v>
+      <c r="DL3" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="DM3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="DN3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="DO3" s="5" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="DO3" s="5">
+        <f>SUM(DJ3:DN3)</f>
+        <v>1</v>
       </c>
       <c r="DP3" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="DS3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT3" s="5">
-        <f>SUM(DM3:DS3)</f>
+        <v>1</v>
+      </c>
+      <c r="DT3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DU3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW3" s="5">
+        <f>SUM(DP3:DV3)</f>
         <v>2</v>
-      </c>
-      <c r="DU3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="DV3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="DW3" s="5" t="n">
-        <v>1</v>
       </c>
       <c r="DX3" s="5" t="n">
         <v>1</v>
@@ -28189,75 +28256,75 @@
         <v>2</v>
       </c>
       <c r="DZ3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EA3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EB3" s="5">
-        <f>SUM(DU3:EA3)</f>
+        <v>1</v>
+      </c>
+      <c r="EB3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="EC3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE3" s="5">
+        <f>SUM(DX3:ED3)</f>
         <v>7</v>
       </c>
-      <c r="EC3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="ED3" s="5" t="n">
+      <c r="EF3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="EG3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="EE3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EF3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EG3" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="EH3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="EI3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="EJ3" s="5">
-        <f>SUM(EC3:EI3)</f>
+      <c r="EJ3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EK3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM3" s="5">
+        <f>SUM(EF3:EL3)</f>
         <v>3</v>
       </c>
-      <c r="EK3" s="5" t="n">
+      <c r="EN3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="EL3" s="5" t="n">
+      <c r="EO3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="EM3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="EN3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="EO3" s="5">
-        <f>SUM(EK3:EN3)</f>
+      <c r="EP3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="EQ3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="ER3" s="5">
+        <f>SUM(EN3:EQ3)</f>
         <v>6</v>
       </c>
-      <c r="EP3" s="5">
-        <f>SUM(DL3,DT3,EB3,EJ3,EO3)</f>
+      <c r="ES3" s="5">
+        <f>SUM(DO3,DW3,EE3,EM3,ER3)</f>
         <v>19</v>
       </c>
-      <c r="EQ3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="ER3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="ES3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="ET3" s="5">
-        <f>SUM(EQ3:ES3)</f>
-        <v>1</v>
+      <c r="ET3" s="15">
+        <f>ES3/440</f>
+        <v>0.04318181818181818</v>
       </c>
       <c r="EU3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EV3" s="5" t="n">
         <v>0</v>
@@ -28265,8 +28332,9 @@
       <c r="EW3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="EX3" s="5" t="n">
-        <v>0</v>
+      <c r="EX3" s="5">
+        <f>SUM(EU3:EW3)</f>
+        <v>1</v>
       </c>
       <c r="EY3" s="5" t="n">
         <v>0</v>
@@ -28277,8 +28345,7 @@
       <c r="FA3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="FB3" s="5">
-        <f>SUM(EU3:FA3)</f>
+      <c r="FB3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="FC3" s="5" t="n">
@@ -28290,7 +28357,8 @@
       <c r="FE3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="FF3" s="5" t="n">
+      <c r="FF3" s="5">
+        <f>SUM(EY3:FE3)</f>
         <v>0</v>
       </c>
       <c r="FG3" s="5" t="n">
@@ -28302,8 +28370,7 @@
       <c r="FI3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="FJ3" s="5">
-        <f>SUM(FC3:FI3)</f>
+      <c r="FJ3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="FK3" s="5" t="n">
@@ -28315,7 +28382,8 @@
       <c r="FM3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="FN3" s="5" t="n">
+      <c r="FN3" s="5">
+        <f>SUM(FG3:FM3)</f>
         <v>0</v>
       </c>
       <c r="FO3" s="5" t="n">
@@ -28327,8 +28395,7 @@
       <c r="FQ3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="FR3" s="5">
-        <f>SUM(FK3:FQ3)</f>
+      <c r="FR3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="FS3" s="5" t="n">
@@ -28340,7 +28407,8 @@
       <c r="FU3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="FV3" s="5" t="n">
+      <c r="FV3" s="5">
+        <f>SUM(FO3:FU3)</f>
         <v>0</v>
       </c>
       <c r="FW3" s="5" t="n">
@@ -28352,88 +28420,88 @@
       <c r="FY3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="FZ3" s="5">
-        <f>SUM(FS3:FY3)</f>
-        <v>0</v>
-      </c>
-      <c r="GA3" s="5">
-        <f>SUM(ET3,FB3,FJ3,FR3,FZ3)</f>
-        <v>1</v>
+      <c r="FZ3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA3" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="GB3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="GC3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD3" s="5">
+        <f>SUM(FW3:GC3)</f>
+        <v>0</v>
+      </c>
+      <c r="GE3" s="5">
+        <f>SUM(EX3,FF3,FN3,FV3,GD3)</f>
+        <v>1</v>
+      </c>
+      <c r="GF3" s="15">
+        <f>GE3/440</f>
+        <v>0.0022727272727272726</v>
+      </c>
+      <c r="GG3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GH3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="GD3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="GE3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GF3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GG3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GH3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GI3" s="5">
-        <f>SUM(GB3:GH3)</f>
+      <c r="GI3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="GJ3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GK3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GL3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN3" s="5">
+        <f>SUM(GG3:GM3)</f>
         <v>3</v>
       </c>
-      <c r="GJ3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="GK3" s="5" t="n">
+      <c r="GO3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="GP3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="GL3" s="5" t="n">
+      <c r="GQ3" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="GM3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="GN3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="GO3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GP3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GQ3" s="5">
-        <f>SUM(GJ3:GP3)</f>
+      <c r="GR3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="GS3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="GT3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV3" s="5">
+        <f>SUM(GO3:GU3)</f>
         <v>8</v>
       </c>
-      <c r="GR3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="GS3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GT3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GU3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GV3" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="GW3" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GX3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="GY3" s="5">
-        <f>SUM(GR3:GX3)</f>
-        <v>1</v>
+      <c r="GY3" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="GZ3" s="5" t="n">
         <v>0</v>
@@ -28442,176 +28510,178 @@
         <v>0</v>
       </c>
       <c r="HB3" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="HC3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HD3" s="5">
+        <f>SUM(GW3:HC3)</f>
+        <v>1</v>
+      </c>
+      <c r="HE3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HF3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HG3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="HH3" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="HD3" s="5" t="n">
+      <c r="HI3" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="HE3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HF3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HG3" s="5">
-        <f>SUM(GZ3:HF3)</f>
+      <c r="HJ3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL3" s="5">
+        <f>SUM(HE3:HK3)</f>
         <v>8</v>
       </c>
-      <c r="HH3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HI3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HJ3" s="5">
-        <f>SUM(HH3:HI3)</f>
-        <v>0</v>
-      </c>
-      <c r="HK3" s="5">
-        <f>SUM(GI3,GQ3,GY3,HG3,HJ3)</f>
+      <c r="HM3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HN3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HO3" s="5">
+        <f>SUM(HM3:HN3)</f>
+        <v>0</v>
+      </c>
+      <c r="HP3" s="5">
+        <f>SUM(GN3,GV3,HD3,HL3,HO3)</f>
         <v>20</v>
       </c>
-      <c r="HL3" s="5" t="n">
+      <c r="HQ3" s="15">
+        <f>HP3/440</f>
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="HR3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="HM3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="HN3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HO3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HP3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HQ3" s="5">
-        <f>SUM(HL3:HP3)</f>
+      <c r="HS3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="HT3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HU3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW3" s="5">
+        <f>SUM(HR3:HV3)</f>
         <v>3</v>
       </c>
-      <c r="HR3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HS3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="HT3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="HU3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HV3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HW3" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="HX3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="HY3" s="5">
-        <f>SUM(HR3:HX3)</f>
+      <c r="HY3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="HZ3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="IA3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IB3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IC3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ID3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IE3" s="5">
+        <f>SUM(HX3:ID3)</f>
         <v>2</v>
       </c>
-      <c r="HZ3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IA3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IB3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IC3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="ID3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IE3" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="IF3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="IG3" s="5">
-        <f>SUM(HZ3:IF3)</f>
+      <c r="IG3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="IH3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="II3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IJ3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IK3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IM3" s="5">
+        <f>SUM(IF3:IL3)</f>
+        <v>0</v>
+      </c>
+      <c r="IN3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="II3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IJ3" s="5" t="n">
+      <c r="IO3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="IK3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IL3" s="5" t="n">
+      <c r="IQ3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IR3" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="IM3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IN3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IO3" s="5">
-        <f>SUM(IH3:IN3)</f>
+      <c r="IS3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IT3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU3" s="5">
+        <f>SUM(IN3:IT3)</f>
         <v>7</v>
       </c>
-      <c r="IP3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IQ3" s="5" t="n">
+      <c r="IV3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IW3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="IR3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IS3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IT3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IU3" s="5">
-        <f>SUM(IP3:IT3)</f>
+      <c r="IX3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IY3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IZ3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="JA3" s="5">
+        <f>SUM(IV3:IZ3)</f>
         <v>2</v>
       </c>
-      <c r="IV3" s="5">
-        <f>SUM(HQ3,HY3,IG3,IO3,IU3)</f>
+      <c r="JB3" s="5">
+        <f>SUM(HW3,IE3,IM3,IU3,JA3)</f>
         <v>14</v>
       </c>
-      <c r="IW3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IX3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IY3" s="5">
-        <f>SUM(IW3:IX3)</f>
-        <v>0</v>
-      </c>
-      <c r="IZ3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JA3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JB3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JC3" s="5" t="n">
-        <v>0</v>
+      <c r="JC3" s="15">
+        <f>JB3/440</f>
+        <v>0.031818181818181815</v>
       </c>
       <c r="JD3" s="5" t="n">
         <v>0</v>
@@ -28619,18 +28689,18 @@
       <c r="JE3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="JF3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JG3" s="5">
-        <f>SUM(IZ3:JF3)</f>
+      <c r="JF3" s="5">
+        <f>SUM(JD3:JE3)</f>
+        <v>0</v>
+      </c>
+      <c r="JG3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="JH3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="JI3" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JJ3" s="5" t="n">
         <v>0</v>
@@ -28639,68 +28709,94 @@
         <v>0</v>
       </c>
       <c r="JL3" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JM3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="JN3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JO3" s="5">
-        <f>SUM(JH3:JN3)</f>
+      <c r="JN3" s="5">
+        <f>SUM(JG3:JM3)</f>
+        <v>0</v>
+      </c>
+      <c r="JO3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="JP3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="JQ3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="JR3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="JS3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="JT3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="JU3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="JV3" s="5">
+        <f>SUM(JO3:JU3)</f>
         <v>2</v>
       </c>
-      <c r="JP3" s="5" t="n">
+      <c r="JW3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="JQ3" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="JR3" s="5" t="n">
+      <c r="JX3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="JY3" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="JS3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JT3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JU3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JV3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JW3" s="5">
-        <f>SUM(JP3:JV3)</f>
+      <c r="JZ3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KA3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KB3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KC3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KD3" s="5">
+        <f>SUM(JW3:KC3)</f>
         <v>5</v>
       </c>
-      <c r="JX3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JY3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JZ3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="KA3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="KB3" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="KC3" s="5">
-        <f>SUM(JX3:KB3)</f>
-        <v>0</v>
-      </c>
-      <c r="KD3" s="5">
-        <f>SUM(IY3,JG3,JO3,JW3,KC3)</f>
+      <c r="KE3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KF3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KG3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KH3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KI3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KJ3" s="5">
+        <f>SUM(KE3:KI3)</f>
+        <v>0</v>
+      </c>
+      <c r="KK3" s="5">
+        <f>SUM(JF3,JN3,JV3,KD3,KJ3)</f>
         <v>7</v>
       </c>
-      <c r="KE3" s="5">
-        <f>SUM(AL3,BT3,DF3,EP3,GA3,HK3,IV3,KD3)</f>
+      <c r="KL3" s="15">
+        <f>KK3/440</f>
+        <v>0.015909090909090907</v>
+      </c>
+      <c r="KM3" s="5">
+        <f>SUM(AL3,BU3,DH3,ES3,GE3,HP3,JB3,KK3)</f>
         <v>63</v>
       </c>
     </row>
@@ -28827,14 +28923,15 @@
         <f>SUM(F4,N4,V4,AD4,AK4)</f>
         <v>0</v>
       </c>
-      <c r="AM4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="5">
-        <f>SUM(AM4:AM4)</f>
-        <v>0</v>
-      </c>
-      <c r="AO4" s="5" t="n">
+      <c r="AM4" s="15">
+        <f>AL4/440</f>
+        <v>0.0</v>
+      </c>
+      <c r="AN4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="5">
+        <f>SUM(AN4:AN4)</f>
         <v>0</v>
       </c>
       <c r="AP4" s="5" t="n">
@@ -28855,11 +28952,11 @@
       <c r="AU4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="AV4" s="5">
-        <f>SUM(AO4:AU4)</f>
-        <v>0</v>
-      </c>
-      <c r="AW4" s="5" t="n">
+      <c r="AV4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" s="5">
+        <f>SUM(AP4:AV4)</f>
         <v>0</v>
       </c>
       <c r="AX4" s="5" t="n">
@@ -28880,11 +28977,11 @@
       <c r="BC4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="BD4" s="5">
-        <f>SUM(AW4:BC4)</f>
-        <v>0</v>
-      </c>
-      <c r="BE4" s="5" t="n">
+      <c r="BD4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE4" s="5">
+        <f>SUM(AX4:BD4)</f>
         <v>0</v>
       </c>
       <c r="BF4" s="5" t="n">
@@ -28905,11 +29002,11 @@
       <c r="BK4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="BL4" s="5">
-        <f>SUM(BE4:BK4)</f>
-        <v>0</v>
-      </c>
-      <c r="BM4" s="5" t="n">
+      <c r="BL4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM4" s="5">
+        <f>SUM(BF4:BL4)</f>
         <v>0</v>
       </c>
       <c r="BN4" s="5" t="n">
@@ -28927,25 +29024,26 @@
       <c r="BR4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="BS4" s="5">
-        <f>SUM(BM4:BR4)</f>
+      <c r="BS4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="BT4" s="5">
-        <f>SUM(AN4,AV4,BD4,BL4,BS4)</f>
-        <v>0</v>
-      </c>
-      <c r="BU4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BV4" s="5">
-        <f>SUM(BU4:BU4)</f>
-        <v>0</v>
+        <f>SUM(BN4:BS4)</f>
+        <v>0</v>
+      </c>
+      <c r="BU4" s="5">
+        <f>SUM(AO4,AW4,BE4,BM4,BT4)</f>
+        <v>0</v>
+      </c>
+      <c r="BV4" s="15">
+        <f>BU4/440</f>
+        <v>0.0</v>
       </c>
       <c r="BW4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="BX4" s="5" t="n">
+      <c r="BX4" s="5">
+        <f>SUM(BW4:BW4)</f>
         <v>0</v>
       </c>
       <c r="BY4" s="5" t="n">
@@ -28963,14 +29061,14 @@
       <c r="CC4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CD4" s="5">
-        <f>SUM(BW4:CC4)</f>
+      <c r="CD4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="CE4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CF4" s="5" t="n">
+      <c r="CF4" s="5">
+        <f>SUM(BY4:CE4)</f>
         <v>0</v>
       </c>
       <c r="CG4" s="5" t="n">
@@ -28988,41 +29086,41 @@
       <c r="CK4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CL4" s="5">
-        <f>SUM(CE4:CK4)</f>
+      <c r="CL4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="CM4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="CN4" s="5" t="n">
+      <c r="CN4" s="5">
+        <f>SUM(CG4:CM4)</f>
         <v>0</v>
       </c>
       <c r="CO4" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CP4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="CQ4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CS4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="CR4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CS4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CT4" s="5">
-        <f>SUM(CM4:CS4)</f>
+      <c r="CT4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CU4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV4" s="5">
+        <f>SUM(CO4:CU4)</f>
         <v>3</v>
       </c>
-      <c r="CU4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="CV4" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="CW4" s="5" t="n">
         <v>0</v>
       </c>
@@ -29038,32 +29136,33 @@
       <c r="DA4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="DB4" s="5">
-        <f>SUM(CU4:DA4)</f>
+      <c r="DB4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="DC4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="DD4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE4" s="5">
-        <f>SUM(DC4:DD4)</f>
-        <v>0</v>
-      </c>
-      <c r="DF4" s="5">
-        <f>SUM(BV4,CD4,CL4,CT4,DB4,DE4)</f>
+      <c r="DD4" s="5">
+        <f>SUM(CW4:DC4)</f>
+        <v>0</v>
+      </c>
+      <c r="DE4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DF4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DG4" s="5">
+        <f>SUM(DE4:DF4)</f>
+        <v>0</v>
+      </c>
+      <c r="DH4" s="5">
+        <f>SUM(BX4,CF4,CN4,CV4,DD4,DG4)</f>
         <v>3</v>
       </c>
-      <c r="DG4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DH4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DI4" s="5" t="n">
-        <v>0</v>
+      <c r="DI4" s="15">
+        <f>DH4/440</f>
+        <v>0.006818181818181818</v>
       </c>
       <c r="DJ4" s="5" t="n">
         <v>0</v>
@@ -29071,8 +29170,7 @@
       <c r="DK4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="DL4" s="5">
-        <f>SUM(DG4:DK4)</f>
+      <c r="DL4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="DM4" s="5" t="n">
@@ -29081,64 +29179,65 @@
       <c r="DN4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="DO4" s="5" t="n">
-        <v>1</v>
+      <c r="DO4" s="5">
+        <f>SUM(DJ4:DN4)</f>
+        <v>0</v>
       </c>
       <c r="DP4" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DQ4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DR4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="DS4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="DT4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="DR4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DS4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DT4" s="5">
-        <f>SUM(DM4:DS4)</f>
+      <c r="DU4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DW4" s="5">
+        <f>SUM(DP4:DV4)</f>
         <v>4</v>
       </c>
-      <c r="DU4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="DV4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DW4" s="5" t="n">
+      <c r="DX4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="DY4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="DX4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="DY4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="DZ4" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="EA4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="EB4" s="5">
-        <f>SUM(DU4:EA4)</f>
+      <c r="EB4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="EC4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ED4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EE4" s="5">
+        <f>SUM(DX4:ED4)</f>
         <v>4</v>
       </c>
-      <c r="EC4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="ED4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE4" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="EF4" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EG4" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EH4" s="5" t="n">
         <v>0</v>
@@ -29146,42 +29245,42 @@
       <c r="EI4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="EJ4" s="5">
-        <f>SUM(EC4:EI4)</f>
+      <c r="EJ4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="EK4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EL4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EM4" s="5">
+        <f>SUM(EF4:EL4)</f>
         <v>2</v>
       </c>
-      <c r="EK4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="EL4" s="5" t="n">
+      <c r="EN4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="EM4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="EN4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="EO4" s="5">
-        <f>SUM(EK4:EN4)</f>
+      <c r="EP4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="EQ4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="ER4" s="5">
+        <f>SUM(EN4:EQ4)</f>
         <v>4</v>
       </c>
-      <c r="EP4" s="5">
-        <f>SUM(DL4,DT4,EB4,EJ4,EO4)</f>
+      <c r="ES4" s="5">
+        <f>SUM(DO4,DW4,EE4,EM4,ER4)</f>
         <v>14</v>
       </c>
-      <c r="EQ4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="ER4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="ES4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="ET4" s="5">
-        <f>SUM(EQ4:ES4)</f>
-        <v>0</v>
+      <c r="ET4" s="15">
+        <f>ES4/440</f>
+        <v>0.031818181818181815</v>
       </c>
       <c r="EU4" s="5" t="n">
         <v>0</v>
@@ -29190,9 +29289,10 @@
         <v>0</v>
       </c>
       <c r="EW4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="EX4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="EX4" s="5">
+        <f>SUM(EU4:EW4)</f>
         <v>0</v>
       </c>
       <c r="EY4" s="5" t="n">
@@ -29202,11 +29302,10 @@
         <v>0</v>
       </c>
       <c r="FA4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FB4" s="5">
-        <f>SUM(EU4:FA4)</f>
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="FB4" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="FC4" s="5" t="n">
         <v>0</v>
@@ -29217,8 +29316,9 @@
       <c r="FE4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="FF4" s="5" t="n">
-        <v>0</v>
+      <c r="FF4" s="5">
+        <f>SUM(EY4:FE4)</f>
+        <v>1</v>
       </c>
       <c r="FG4" s="5" t="n">
         <v>0</v>
@@ -29229,8 +29329,7 @@
       <c r="FI4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="FJ4" s="5">
-        <f>SUM(FC4:FI4)</f>
+      <c r="FJ4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="FK4" s="5" t="n">
@@ -29240,9 +29339,10 @@
         <v>0</v>
       </c>
       <c r="FM4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="FN4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="FN4" s="5">
+        <f>SUM(FG4:FM4)</f>
         <v>0</v>
       </c>
       <c r="FO4" s="5" t="n">
@@ -29252,11 +29352,10 @@
         <v>0</v>
       </c>
       <c r="FQ4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="FR4" s="5">
-        <f>SUM(FK4:FQ4)</f>
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="FR4" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="FS4" s="5" t="n">
         <v>0</v>
@@ -29267,8 +29366,9 @@
       <c r="FU4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="FV4" s="5" t="n">
-        <v>0</v>
+      <c r="FV4" s="5">
+        <f>SUM(FO4:FU4)</f>
+        <v>1</v>
       </c>
       <c r="FW4" s="5" t="n">
         <v>0</v>
@@ -29279,355 +29379,383 @@
       <c r="FY4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="FZ4" s="5">
-        <f>SUM(FS4:FY4)</f>
-        <v>0</v>
-      </c>
-      <c r="GA4" s="5">
-        <f>SUM(ET4,FB4,FJ4,FR4,FZ4)</f>
+      <c r="FZ4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GA4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GB4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GC4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GD4" s="5">
+        <f>SUM(FW4:GC4)</f>
+        <v>0</v>
+      </c>
+      <c r="GE4" s="5">
+        <f>SUM(EX4,FF4,FN4,FV4,GD4)</f>
         <v>2</v>
       </c>
-      <c r="GB4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GC4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="GD4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="GE4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GF4" s="5" t="n">
-        <v>1</v>
+      <c r="GF4" s="15">
+        <f>GE4/440</f>
+        <v>0.004545454545454545</v>
       </c>
       <c r="GG4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="GH4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GI4" s="5">
-        <f>SUM(GB4:GH4)</f>
+        <v>1</v>
+      </c>
+      <c r="GI4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="GJ4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GK4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="GL4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GM4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GN4" s="5">
+        <f>SUM(GG4:GM4)</f>
         <v>3</v>
       </c>
-      <c r="GJ4" s="5" t="n">
+      <c r="GO4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="GK4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GL4" s="5" t="n">
+      <c r="GP4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GQ4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="GM4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="GN4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="GO4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GP4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GQ4" s="5">
-        <f>SUM(GJ4:GP4)</f>
+      <c r="GR4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="GS4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="GT4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GU4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="GV4" s="5">
+        <f>SUM(GO4:GU4)</f>
         <v>7</v>
       </c>
-      <c r="GR4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GS4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="GT4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="GU4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GV4" s="5" t="n">
-        <v>1</v>
-      </c>
       <c r="GW4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="GX4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="GY4" s="5">
-        <f>SUM(GR4:GX4)</f>
+        <v>1</v>
+      </c>
+      <c r="GY4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="GZ4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HA4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="HB4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HC4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HD4" s="5">
+        <f>SUM(GW4:HC4)</f>
         <v>3</v>
       </c>
-      <c r="GZ4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="HA4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="HB4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HC4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="HD4" s="5" t="n">
+      <c r="HE4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="HF4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="HG4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HH4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="HI4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="HE4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HF4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HG4" s="5">
-        <f>SUM(GZ4:HF4)</f>
+      <c r="HJ4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HK4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HL4" s="5">
+        <f>SUM(HE4:HK4)</f>
         <v>5</v>
       </c>
-      <c r="HH4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="HI4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="HJ4" s="5">
-        <f>SUM(HH4:HI4)</f>
+      <c r="HM4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="HN4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="HO4" s="5">
+        <f>SUM(HM4:HN4)</f>
         <v>2</v>
       </c>
-      <c r="HK4" s="5">
-        <f>SUM(GI4,GQ4,GY4,HG4,HJ4)</f>
+      <c r="HP4" s="5">
+        <f>SUM(GN4,GV4,HD4,HL4,HO4)</f>
         <v>20</v>
       </c>
-      <c r="HL4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="HM4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="HN4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="HO4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HP4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HQ4" s="5">
-        <f>SUM(HL4:HP4)</f>
+      <c r="HQ4" s="15">
+        <f>HP4/440</f>
+        <v>0.045454545454545456</v>
+      </c>
+      <c r="HR4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="HS4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="HT4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="HU4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HV4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HW4" s="5">
+        <f>SUM(HR4:HV4)</f>
         <v>3</v>
       </c>
-      <c r="HR4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HS4" s="5" t="n">
+      <c r="HX4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="HY4" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="HT4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="HU4" s="5" t="n">
+      <c r="HZ4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="IA4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="HV4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="HW4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HX4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="HY4" s="5">
-        <f>SUM(HR4:HX4)</f>
+      <c r="IB4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="IC4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="ID4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IE4" s="5">
+        <f>SUM(HX4:ID4)</f>
         <v>7</v>
       </c>
-      <c r="HZ4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="IA4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IB4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="IC4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="ID4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="IE4" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="IF4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IG4" s="5">
-        <f>SUM(HZ4:IF4)</f>
+        <v>1</v>
+      </c>
+      <c r="IG4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IH4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="II4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="IJ4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="IK4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IL4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IM4" s="5">
+        <f>SUM(IF4:IL4)</f>
         <v>4</v>
       </c>
-      <c r="IH4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="II4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IJ4" s="5" t="n">
+      <c r="IN4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IO4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IP4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="IK4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="IL4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IM4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IN4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IO4" s="5">
-        <f>SUM(IH4:IN4)</f>
+      <c r="IQ4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="IR4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IS4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IT4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="IU4" s="5">
+        <f>SUM(IN4:IT4)</f>
         <v>3</v>
       </c>
-      <c r="IP4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="IQ4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="IR4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="IS4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="IT4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="IU4" s="5">
-        <f>SUM(IP4:IT4)</f>
+      <c r="IV4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="IW4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="IX4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="IY4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="IZ4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="JA4" s="5">
+        <f>SUM(IV4:IZ4)</f>
         <v>5</v>
       </c>
-      <c r="IV4" s="5">
-        <f>SUM(HQ4,HY4,IG4,IO4,IU4)</f>
+      <c r="JB4" s="5">
+        <f>SUM(HW4,IE4,IM4,IU4,JA4)</f>
         <v>22</v>
       </c>
-      <c r="IW4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IX4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="IY4" s="5">
-        <f>SUM(IW4:IX4)</f>
-        <v>0</v>
-      </c>
-      <c r="IZ4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JA4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="JB4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JC4" s="5" t="n">
-        <v>1</v>
+      <c r="JC4" s="15">
+        <f>JB4/440</f>
+        <v>0.05</v>
       </c>
       <c r="JD4" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JE4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="JF4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JG4" s="5">
-        <f>SUM(IZ4:JF4)</f>
-        <v>4</v>
+      <c r="JF4" s="5">
+        <f>SUM(JD4:JE4)</f>
+        <v>0</v>
+      </c>
+      <c r="JG4" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="JH4" s="5" t="n">
         <v>2</v>
       </c>
       <c r="JI4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="JJ4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="JK4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="JL4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="JM4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="JN4" s="5">
+        <f>SUM(JG4:JM4)</f>
+        <v>4</v>
+      </c>
+      <c r="JO4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="JJ4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="JK4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="JL4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="JM4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JN4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JO4" s="5">
-        <f>SUM(JH4:JN4)</f>
+      <c r="JP4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="JQ4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="JR4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="JS4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="JT4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="JU4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="JV4" s="5">
+        <f>SUM(JO4:JU4)</f>
         <v>7</v>
       </c>
-      <c r="JP4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JQ4" s="5" t="n">
+      <c r="JW4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="JX4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="JR4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="JS4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JT4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="JU4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JV4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JW4" s="5">
-        <f>SUM(JP4:JV4)</f>
+      <c r="JY4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="JZ4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KA4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="KB4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KC4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KD4" s="5">
+        <f>SUM(JW4:KC4)</f>
         <v>4</v>
       </c>
-      <c r="JX4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JY4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="JZ4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="KA4" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="KB4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="KC4" s="5">
-        <f>SUM(JX4:KB4)</f>
-        <v>1</v>
-      </c>
-      <c r="KD4" s="5">
-        <f>SUM(IY4,JG4,JO4,JW4,KC4)</f>
+      <c r="KE4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KF4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KG4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KH4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KI4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="KJ4" s="5">
+        <f>SUM(KE4:KI4)</f>
+        <v>1</v>
+      </c>
+      <c r="KK4" s="5">
+        <f>SUM(JF4,JN4,JV4,KD4,KJ4)</f>
         <v>16</v>
       </c>
-      <c r="KE4" s="5">
-        <f>SUM(AL4,BT4,DF4,EP4,GA4,HK4,IV4,KD4)</f>
+      <c r="KL4" s="15">
+        <f>KK4/440</f>
+        <v>0.03636363636363636</v>
+      </c>
+      <c r="KM4" s="5">
+        <f>SUM(AL4,BU4,DH4,ES4,GE4,HP4,JB4,KK4)</f>
         <v>77</v>
       </c>
     </row>
@@ -29785,9 +29913,9 @@
         <f>SUM(AL3,AL4)</f>
         <v>0</v>
       </c>
-      <c r="AM5" s="7">
-        <f>SUM(AM3,AM4)</f>
-        <v>0</v>
+      <c r="AM5" s="16">
+        <f>AL5/880</f>
+        <v>0.0</v>
       </c>
       <c r="AN5" s="7">
         <f>SUM(AN3,AN4)</f>
@@ -29925,9 +30053,9 @@
         <f>SUM(BU3,BU4)</f>
         <v>0</v>
       </c>
-      <c r="BV5" s="7">
-        <f>SUM(BV3,BV4)</f>
-        <v>0</v>
+      <c r="BV5" s="16">
+        <f>BU5/880</f>
+        <v>0.0</v>
       </c>
       <c r="BW5" s="7">
         <f>SUM(BW3,BW4)</f>
@@ -29995,7 +30123,7 @@
       </c>
       <c r="CM5" s="7">
         <f>SUM(CM3,CM4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN5" s="7">
         <f>SUM(CN3,CN4)</f>
@@ -30003,7 +30131,7 @@
       </c>
       <c r="CO5" s="7">
         <f>SUM(CO3,CO4)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="CP5" s="7">
         <f>SUM(CP3,CP4)</f>
@@ -30019,11 +30147,11 @@
       </c>
       <c r="CS5" s="7">
         <f>SUM(CS3,CS4)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CT5" s="7">
         <f>SUM(CT3,CT4)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="CU5" s="7">
         <f>SUM(CU3,CU4)</f>
@@ -30031,7 +30159,7 @@
       </c>
       <c r="CV5" s="7">
         <f>SUM(CV3,CV4)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="CW5" s="7">
         <f>SUM(CW3,CW4)</f>
@@ -30071,23 +30199,23 @@
       </c>
       <c r="DF5" s="7">
         <f>SUM(DF3,DF4)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="DG5" s="7">
         <f>SUM(DG3,DG4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DH5" s="7">
         <f>SUM(DH3,DH4)</f>
-        <v>0</v>
-      </c>
-      <c r="DI5" s="7">
-        <f>SUM(DI3,DI4)</f>
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c r="DI5" s="16">
+        <f>DH5/880</f>
+        <v>0.005681818181818182</v>
       </c>
       <c r="DJ5" s="7">
         <f>SUM(DJ3,DJ4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DK5" s="7">
         <f>SUM(DK3,DK4)</f>
@@ -30095,7 +30223,7 @@
       </c>
       <c r="DL5" s="7">
         <f>SUM(DL3,DL4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DM5" s="7">
         <f>SUM(DM3,DM4)</f>
@@ -30103,7 +30231,7 @@
       </c>
       <c r="DN5" s="7">
         <f>SUM(DN3,DN4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DO5" s="7">
         <f>SUM(DO3,DO4)</f>
@@ -30111,75 +30239,75 @@
       </c>
       <c r="DP5" s="7">
         <f>SUM(DP3,DP4)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DQ5" s="7">
         <f>SUM(DQ3,DQ4)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="DR5" s="7">
         <f>SUM(DR3,DR4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS5" s="7">
         <f>SUM(DS3,DS4)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="DT5" s="7">
         <f>SUM(DT3,DT4)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="DU5" s="7">
         <f>SUM(DU3,DU4)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DV5" s="7">
         <f>SUM(DV3,DV4)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="DW5" s="7">
         <f>SUM(DW3,DW4)</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="DX5" s="7">
         <f>SUM(DX3,DX4)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="DY5" s="7">
         <f>SUM(DY3,DY4)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="DZ5" s="7">
         <f>SUM(DZ3,DZ4)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="EA5" s="7">
         <f>SUM(EA3,EA4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EB5" s="7">
         <f>SUM(EB3,EB4)</f>
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="EC5" s="7">
         <f>SUM(EC3,EC4)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="ED5" s="7">
         <f>SUM(ED3,ED4)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="EE5" s="7">
         <f>SUM(EE3,EE4)</f>
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="EF5" s="7">
         <f>SUM(EF3,EF4)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="EG5" s="7">
         <f>SUM(EG3,EG4)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="EH5" s="7">
         <f>SUM(EH3,EH4)</f>
@@ -30191,19 +30319,19 @@
       </c>
       <c r="EJ5" s="7">
         <f>SUM(EJ3,EJ4)</f>
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="EK5" s="7">
         <f>SUM(EK3,EK4)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="EL5" s="7">
         <f>SUM(EL3,EL4)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="EM5" s="7">
         <f>SUM(EM3,EM4)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="EN5" s="7">
         <f>SUM(EN3,EN4)</f>
@@ -30211,31 +30339,31 @@
       </c>
       <c r="EO5" s="7">
         <f>SUM(EO3,EO4)</f>
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="EP5" s="7">
         <f>SUM(EP3,EP4)</f>
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="EQ5" s="7">
         <f>SUM(EQ3,EQ4)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="ER5" s="7">
         <f>SUM(ER3,ER4)</f>
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="ES5" s="7">
         <f>SUM(ES3,ES4)</f>
-        <v>0</v>
-      </c>
-      <c r="ET5" s="7">
-        <f>SUM(ET3,ET4)</f>
-        <v>1</v>
+        <v>33</v>
+      </c>
+      <c r="ET5" s="16">
+        <f>ES5/880</f>
+        <v>0.0375</v>
       </c>
       <c r="EU5" s="7">
         <f>SUM(EU3,EU4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EV5" s="7">
         <f>SUM(EV3,EV4)</f>
@@ -30243,11 +30371,11 @@
       </c>
       <c r="EW5" s="7">
         <f>SUM(EW3,EW4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="EX5" s="7">
         <f>SUM(EX3,EX4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="EY5" s="7">
         <f>SUM(EY3,EY4)</f>
@@ -30259,11 +30387,11 @@
       </c>
       <c r="FA5" s="7">
         <f>SUM(FA3,FA4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FB5" s="7">
         <f>SUM(FB3,FB4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FC5" s="7">
         <f>SUM(FC3,FC4)</f>
@@ -30279,7 +30407,7 @@
       </c>
       <c r="FF5" s="7">
         <f>SUM(FF3,FF4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FG5" s="7">
         <f>SUM(FG3,FG4)</f>
@@ -30307,7 +30435,7 @@
       </c>
       <c r="FM5" s="7">
         <f>SUM(FM3,FM4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FN5" s="7">
         <f>SUM(FN3,FN4)</f>
@@ -30323,11 +30451,11 @@
       </c>
       <c r="FQ5" s="7">
         <f>SUM(FQ3,FQ4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FR5" s="7">
         <f>SUM(FR3,FR4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="FS5" s="7">
         <f>SUM(FS3,FS4)</f>
@@ -30343,7 +30471,7 @@
       </c>
       <c r="FV5" s="7">
         <f>SUM(FV3,FV4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="FW5" s="7">
         <f>SUM(FW3,FW4)</f>
@@ -30363,7 +30491,7 @@
       </c>
       <c r="GA5" s="7">
         <f>SUM(GA3,GA4)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="GB5" s="7">
         <f>SUM(GB3,GB4)</f>
@@ -30371,19 +30499,19 @@
       </c>
       <c r="GC5" s="7">
         <f>SUM(GC3,GC4)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="GD5" s="7">
         <f>SUM(GD3,GD4)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="GE5" s="7">
         <f>SUM(GE3,GE4)</f>
-        <v>0</v>
-      </c>
-      <c r="GF5" s="7">
-        <f>SUM(GF3,GF4)</f>
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="GF5" s="16">
+        <f>GE5/880</f>
+        <v>0.003409090909090909</v>
       </c>
       <c r="GG5" s="7">
         <f>SUM(GG3,GG4)</f>
@@ -30391,55 +30519,55 @@
       </c>
       <c r="GH5" s="7">
         <f>SUM(GH3,GH4)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="GI5" s="7">
         <f>SUM(GI3,GI4)</f>
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="GJ5" s="7">
         <f>SUM(GJ3,GJ4)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="GK5" s="7">
         <f>SUM(GK3,GK4)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="GL5" s="7">
         <f>SUM(GL3,GL4)</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="GM5" s="7">
         <f>SUM(GM3,GM4)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="GN5" s="7">
         <f>SUM(GN3,GN4)</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="GO5" s="7">
         <f>SUM(GO3,GO4)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="GP5" s="7">
         <f>SUM(GP3,GP4)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="GQ5" s="7">
         <f>SUM(GQ3,GQ4)</f>
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="GR5" s="7">
         <f>SUM(GR3,GR4)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="GS5" s="7">
         <f>SUM(GS3,GS4)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="GT5" s="7">
         <f>SUM(GT3,GT4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="GU5" s="7">
         <f>SUM(GU3,GU4)</f>
@@ -30447,23 +30575,23 @@
       </c>
       <c r="GV5" s="7">
         <f>SUM(GV3,GV4)</f>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="GW5" s="7">
         <f>SUM(GW3,GW4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GX5" s="7">
         <f>SUM(GX3,GX4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="GY5" s="7">
         <f>SUM(GY3,GY4)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="GZ5" s="7">
         <f>SUM(GZ3,GZ4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="HA5" s="7">
         <f>SUM(HA3,HA4)</f>
@@ -30471,51 +30599,51 @@
       </c>
       <c r="HB5" s="7">
         <f>SUM(HB3,HB4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="HC5" s="7">
         <f>SUM(HC3,HC4)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="HD5" s="7">
         <f>SUM(HD3,HD4)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="HE5" s="7">
         <f>SUM(HE3,HE4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="HF5" s="7">
         <f>SUM(HF3,HF4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="HG5" s="7">
         <f>SUM(HG3,HG4)</f>
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="HH5" s="7">
         <f>SUM(HH3,HH4)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="HI5" s="7">
         <f>SUM(HI3,HI4)</f>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="HJ5" s="7">
         <f>SUM(HJ3,HJ4)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="HK5" s="7">
         <f>SUM(HK3,HK4)</f>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="HL5" s="7">
         <f>SUM(HL3,HL4)</f>
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="HM5" s="7">
         <f>SUM(HM3,HM4)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="HN5" s="7">
         <f>SUM(HN3,HN4)</f>
@@ -30523,39 +30651,39 @@
       </c>
       <c r="HO5" s="7">
         <f>SUM(HO3,HO4)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="HP5" s="7">
         <f>SUM(HP3,HP4)</f>
-        <v>0</v>
-      </c>
-      <c r="HQ5" s="7">
-        <f>SUM(HQ3,HQ4)</f>
-        <v>6</v>
+        <v>40</v>
+      </c>
+      <c r="HQ5" s="16">
+        <f>HP5/880</f>
+        <v>0.045454545454545456</v>
       </c>
       <c r="HR5" s="7">
         <f>SUM(HR3,HR4)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="HS5" s="7">
         <f>SUM(HS3,HS4)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="HT5" s="7">
         <f>SUM(HT3,HT4)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="HU5" s="7">
         <f>SUM(HU3,HU4)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="HV5" s="7">
         <f>SUM(HV3,HV4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="HW5" s="7">
         <f>SUM(HW3,HW4)</f>
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="HX5" s="7">
         <f>SUM(HX3,HX4)</f>
@@ -30563,15 +30691,15 @@
       </c>
       <c r="HY5" s="7">
         <f>SUM(HY3,HY4)</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="HZ5" s="7">
         <f>SUM(HZ3,HZ4)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="IA5" s="7">
         <f>SUM(IA3,IA4)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IB5" s="7">
         <f>SUM(IB3,IB4)</f>
@@ -30579,115 +30707,115 @@
       </c>
       <c r="IC5" s="7">
         <f>SUM(IC3,IC4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="ID5" s="7">
         <f>SUM(ID3,ID4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IE5" s="7">
         <f>SUM(IE3,IE4)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="IF5" s="7">
         <f>SUM(IF3,IF4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IG5" s="7">
         <f>SUM(IG3,IG4)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="IH5" s="7">
         <f>SUM(IH3,IH4)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="II5" s="7">
         <f>SUM(II3,II4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IJ5" s="7">
         <f>SUM(IJ3,IJ4)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="IK5" s="7">
         <f>SUM(IK3,IK4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IL5" s="7">
         <f>SUM(IL3,IL4)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="IM5" s="7">
         <f>SUM(IM3,IM4)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="IN5" s="7">
         <f>SUM(IN3,IN4)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="IO5" s="7">
         <f>SUM(IO3,IO4)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="IP5" s="7">
         <f>SUM(IP3,IP4)</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="IQ5" s="7">
         <f>SUM(IQ3,IQ4)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="IR5" s="7">
         <f>SUM(IR3,IR4)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="IS5" s="7">
         <f>SUM(IS3,IS4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IT5" s="7">
         <f>SUM(IT3,IT4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="IU5" s="7">
         <f>SUM(IU3,IU4)</f>
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="IV5" s="7">
         <f>SUM(IV3,IV4)</f>
-        <v>36</v>
+        <v>1</v>
       </c>
       <c r="IW5" s="7">
         <f>SUM(IW3,IW4)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="IX5" s="7">
         <f>SUM(IX3,IX4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IY5" s="7">
         <f>SUM(IY3,IY4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="IZ5" s="7">
         <f>SUM(IZ3,IZ4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JA5" s="7">
         <f>SUM(JA3,JA4)</f>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="JB5" s="7">
         <f>SUM(JB3,JB4)</f>
-        <v>0</v>
-      </c>
-      <c r="JC5" s="7">
-        <f>SUM(JC3,JC4)</f>
-        <v>1</v>
+        <v>36</v>
+      </c>
+      <c r="JC5" s="16">
+        <f>JB5/880</f>
+        <v>0.04090909090909091</v>
       </c>
       <c r="JD5" s="7">
         <f>SUM(JD3,JD4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JE5" s="7">
         <f>SUM(JE3,JE4)</f>
@@ -30699,7 +30827,7 @@
       </c>
       <c r="JG5" s="7">
         <f>SUM(JG3,JG4)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="JH5" s="7">
         <f>SUM(JH3,JH4)</f>
@@ -30707,7 +30835,7 @@
       </c>
       <c r="JI5" s="7">
         <f>SUM(JI3,JI4)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="JJ5" s="7">
         <f>SUM(JJ3,JJ4)</f>
@@ -30719,7 +30847,7 @@
       </c>
       <c r="JL5" s="7">
         <f>SUM(JL3,JL4)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="JM5" s="7">
         <f>SUM(JM3,JM4)</f>
@@ -30727,31 +30855,31 @@
       </c>
       <c r="JN5" s="7">
         <f>SUM(JN3,JN4)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="JO5" s="7">
         <f>SUM(JO3,JO4)</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="JP5" s="7">
         <f>SUM(JP3,JP4)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="JQ5" s="7">
         <f>SUM(JQ3,JQ4)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="JR5" s="7">
         <f>SUM(JR3,JR4)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="JS5" s="7">
         <f>SUM(JS3,JS4)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="JT5" s="7">
         <f>SUM(JT3,JT4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JU5" s="7">
         <f>SUM(JU3,JU4)</f>
@@ -30759,19 +30887,19 @@
       </c>
       <c r="JV5" s="7">
         <f>SUM(JV3,JV4)</f>
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="JW5" s="7">
         <f>SUM(JW3,JW4)</f>
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="JX5" s="7">
         <f>SUM(JX3,JX4)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="JY5" s="7">
         <f>SUM(JY3,JY4)</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="JZ5" s="7">
         <f>SUM(JZ3,JZ4)</f>
@@ -30779,28 +30907,60 @@
       </c>
       <c r="KA5" s="7">
         <f>SUM(KA3,KA4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="KB5" s="7">
         <f>SUM(KB3,KB4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="KC5" s="7">
         <f>SUM(KC3,KC4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="KD5" s="7">
         <f>SUM(KD3,KD4)</f>
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="KE5" s="7">
         <f>SUM(KE3,KE4)</f>
+        <v>0</v>
+      </c>
+      <c r="KF5" s="7">
+        <f>SUM(KF3,KF4)</f>
+        <v>0</v>
+      </c>
+      <c r="KG5" s="7">
+        <f>SUM(KG3,KG4)</f>
+        <v>0</v>
+      </c>
+      <c r="KH5" s="7">
+        <f>SUM(KH3,KH4)</f>
+        <v>0</v>
+      </c>
+      <c r="KI5" s="7">
+        <f>SUM(KI3,KI4)</f>
+        <v>1</v>
+      </c>
+      <c r="KJ5" s="7">
+        <f>SUM(KJ3,KJ4)</f>
+        <v>1</v>
+      </c>
+      <c r="KK5" s="7">
+        <f>SUM(KK3,KK4)</f>
+        <v>23</v>
+      </c>
+      <c r="KL5" s="16">
+        <f>KK5/880</f>
+        <v>0.026136363636363635</v>
+      </c>
+      <c r="KM5" s="7">
+        <f>SUM(KM3,KM4)</f>
         <v>140</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:KE1"/>
+    <mergeCell ref="B1:KM1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30821,19 +30981,19 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="17" t="inlineStr">
         <is>
           <t>Minimum Annual KPIs</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="16" t="inlineStr">
+      <c r="A3" s="18" t="inlineStr">
         <is>
           <t>KPI</t>
         </is>
       </c>
-      <c r="B3" s="16" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>Minimum Target</t>
         </is>
@@ -30895,33 +31055,33 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>460/year (~38/month, ~9/week)</t>
+          <t>440/year per BDM (~37/month, ~8/week)</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Weekly figures assume a 5-day work week. These are minimum expectations, not aspirational targets.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Detailed Expectations</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="18" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>• The 36-referred-to-12-retained ratio is deliberate - it sets an explicit ~33% minimum conversion rate, tracked monthly and annually, not just at year-end</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>• Activity volume (calls, meetings, presentations) is a leading indicator, not the target - hitting activity minimums while missing the 12-retained-clients/year floor is not meeting the mandate</t>
         </is>

--- a/reports/reports.xlsx
+++ b/reports/reports.xlsx
@@ -537,7 +537,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:KE11"/>
+  <dimension ref="A1:KF11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -828,9 +828,10 @@
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="286" max="286"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="287" max="287"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="288" max="288"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="289" max="289"/>
-    <col collapsed="1" width="13" customWidth="1" min="290" max="290"/>
-    <col width="14" customWidth="1" min="291" max="291"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="289" max="289"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="290" max="290"/>
+    <col collapsed="1" width="13" customWidth="1" min="291" max="291"/>
+    <col width="14" customWidth="1" min="292" max="292"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1133,6 +1134,7 @@
       <c r="KC1" s="1" t="n"/>
       <c r="KD1" s="1" t="n"/>
       <c r="KE1" s="1" t="n"/>
+      <c r="KF1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n"/>
@@ -2573,15 +2575,20 @@
       </c>
       <c r="KC2" s="1" t="inlineStr">
         <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="KD2" s="1" t="inlineStr">
+        <is>
           <t>W5 Aug</t>
         </is>
       </c>
-      <c r="KD2" s="1" t="inlineStr">
+      <c r="KE2" s="1" t="inlineStr">
         <is>
           <t>Aug Total</t>
         </is>
       </c>
-      <c r="KE2" s="1" t="inlineStr">
+      <c r="KF2" s="1" t="inlineStr">
         <is>
           <t>YTD Total</t>
         </is>
@@ -3751,6 +3758,10 @@
       </c>
       <c r="KE3" s="3">
         <f>SUM(KE4,KE5)</f>
+        <v>0</v>
+      </c>
+      <c r="KF3" s="3">
+        <f>SUM(KF4,KF5)</f>
         <v>1</v>
       </c>
     </row>
@@ -4668,16 +4679,19 @@
       <c r="KB4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="KC4" s="5">
-        <f>SUM(JX4:KB4)</f>
+      <c r="KC4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="KD4" s="5">
-        <f>SUM(IY4,JG4,JO4,JW4,KC4)</f>
+        <f>SUM(JX4:KC4)</f>
         <v>0</v>
       </c>
       <c r="KE4" s="5">
-        <f>SUM(AL4,BT4,DF4,EP4,GA4,HK4,IV4,KD4)</f>
+        <f>SUM(IY4,JG4,JO4,JW4,KD4)</f>
+        <v>0</v>
+      </c>
+      <c r="KF4" s="5">
+        <f>SUM(AL4,BT4,DF4,EP4,GA4,HK4,IV4,KE4)</f>
         <v>0</v>
       </c>
     </row>
@@ -5595,16 +5609,19 @@
       <c r="KB5" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="KC5" s="5">
-        <f>SUM(JX5:KB5)</f>
+      <c r="KC5" s="5" t="n">
         <v>0</v>
       </c>
       <c r="KD5" s="5">
-        <f>SUM(IY5,JG5,JO5,JW5,KC5)</f>
+        <f>SUM(JX5:KC5)</f>
         <v>0</v>
       </c>
       <c r="KE5" s="5">
-        <f>SUM(AL5,BT5,DF5,EP5,GA5,HK5,IV5,KD5)</f>
+        <f>SUM(IY5,JG5,JO5,JW5,KD5)</f>
+        <v>0</v>
+      </c>
+      <c r="KF5" s="5">
+        <f>SUM(AL5,BT5,DF5,EP5,GA5,HK5,IV5,KE5)</f>
         <v>1</v>
       </c>
     </row>
@@ -6772,6 +6789,10 @@
       </c>
       <c r="KE6" s="3">
         <f>SUM(KE7,KE8)</f>
+        <v>0</v>
+      </c>
+      <c r="KF6" s="3">
+        <f>SUM(KF7,KF8)</f>
         <v>1</v>
       </c>
     </row>
@@ -7689,16 +7710,19 @@
       <c r="KB7" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="KC7" s="5">
-        <f>SUM(JX7:KB7)</f>
+      <c r="KC7" s="5" t="n">
         <v>0</v>
       </c>
       <c r="KD7" s="5">
-        <f>SUM(IY7,JG7,JO7,JW7,KC7)</f>
+        <f>SUM(JX7:KC7)</f>
         <v>0</v>
       </c>
       <c r="KE7" s="5">
-        <f>SUM(AL7,BT7,DF7,EP7,GA7,HK7,IV7,KD7)</f>
+        <f>SUM(IY7,JG7,JO7,JW7,KD7)</f>
+        <v>0</v>
+      </c>
+      <c r="KF7" s="5">
+        <f>SUM(AL7,BT7,DF7,EP7,GA7,HK7,IV7,KE7)</f>
         <v>1</v>
       </c>
     </row>
@@ -8616,16 +8640,19 @@
       <c r="KB8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="KC8" s="5">
-        <f>SUM(JX8:KB8)</f>
+      <c r="KC8" s="5" t="n">
         <v>0</v>
       </c>
       <c r="KD8" s="5">
-        <f>SUM(IY8,JG8,JO8,JW8,KC8)</f>
+        <f>SUM(JX8:KC8)</f>
         <v>0</v>
       </c>
       <c r="KE8" s="5">
-        <f>SUM(AL8,BT8,DF8,EP8,GA8,HK8,IV8,KD8)</f>
+        <f>SUM(IY8,JG8,JO8,JW8,KD8)</f>
+        <v>0</v>
+      </c>
+      <c r="KF8" s="5">
+        <f>SUM(AL8,BT8,DF8,EP8,GA8,HK8,IV8,KE8)</f>
         <v>0</v>
       </c>
     </row>
@@ -9793,6 +9820,10 @@
       </c>
       <c r="KE9" s="7">
         <f>SUM(KE3,KE6)</f>
+        <v>0</v>
+      </c>
+      <c r="KF9" s="7">
+        <f>SUM(KF3,KF6)</f>
         <v>2</v>
       </c>
     </row>
@@ -10118,12 +10149,13 @@
       <c r="KA10" s="9" t="n"/>
       <c r="KB10" s="9" t="n"/>
       <c r="KC10" s="9" t="n"/>
-      <c r="KD10" s="10" t="inlineStr">
+      <c r="KD10" s="9" t="n"/>
+      <c r="KE10" s="10" t="inlineStr">
         <is>
           <t>8/12</t>
         </is>
       </c>
-      <c r="KE10" s="10" t="inlineStr">
+      <c r="KF10" s="10" t="inlineStr">
         <is>
           <t>8/12</t>
         </is>
@@ -10451,12 +10483,13 @@
       <c r="KA11" s="9" t="n"/>
       <c r="KB11" s="9" t="n"/>
       <c r="KC11" s="9" t="n"/>
-      <c r="KD11" s="10" t="inlineStr">
+      <c r="KD11" s="9" t="n"/>
+      <c r="KE11" s="10" t="inlineStr">
         <is>
           <t>8/12</t>
         </is>
       </c>
-      <c r="KE11" s="10" t="inlineStr">
+      <c r="KF11" s="10" t="inlineStr">
         <is>
           <t>8/12</t>
         </is>
@@ -10464,7 +10497,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:KE1"/>
+    <mergeCell ref="B1:KF1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10477,7 +10510,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:KE5"/>
+  <dimension ref="A1:KF5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -10768,9 +10801,10 @@
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="286" max="286"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="287" max="287"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="288" max="288"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="289" max="289"/>
-    <col collapsed="1" width="13" customWidth="1" min="290" max="290"/>
-    <col width="14" customWidth="1" min="291" max="291"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="289" max="289"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="290" max="290"/>
+    <col collapsed="1" width="13" customWidth="1" min="291" max="291"/>
+    <col width="14" customWidth="1" min="292" max="292"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11073,6 +11107,7 @@
       <c r="KC1" s="11" t="n"/>
       <c r="KD1" s="11" t="n"/>
       <c r="KE1" s="11" t="n"/>
+      <c r="KF1" s="11" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n"/>
@@ -12513,15 +12548,20 @@
       </c>
       <c r="KC2" s="11" t="inlineStr">
         <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="KD2" s="11" t="inlineStr">
+        <is>
           <t>W5 Aug</t>
         </is>
       </c>
-      <c r="KD2" s="11" t="inlineStr">
+      <c r="KE2" s="11" t="inlineStr">
         <is>
           <t>Aug Total</t>
         </is>
       </c>
-      <c r="KE2" s="11" t="inlineStr">
+      <c r="KF2" s="11" t="inlineStr">
         <is>
           <t>YTD Total</t>
         </is>
@@ -13441,16 +13481,19 @@
       <c r="KB3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="KC3" s="5">
-        <f>SUM(JX3:KB3)</f>
+      <c r="KC3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="KD3" s="5">
-        <f>SUM(IY3,JG3,JO3,JW3,KC3)</f>
+        <f>SUM(JX3:KC3)</f>
         <v>0</v>
       </c>
       <c r="KE3" s="5">
-        <f>SUM(AL3,BT3,DF3,EP3,GA3,HK3,IV3,KD3)</f>
+        <f>SUM(IY3,JG3,JO3,JW3,KD3)</f>
+        <v>0</v>
+      </c>
+      <c r="KF3" s="5">
+        <f>SUM(AL3,BT3,DF3,EP3,GA3,HK3,IV3,KE3)</f>
         <v>16</v>
       </c>
     </row>
@@ -14368,16 +14411,19 @@
       <c r="KB4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="KC4" s="5">
-        <f>SUM(JX4:KB4)</f>
+      <c r="KC4" s="5" t="n">
         <v>0</v>
       </c>
       <c r="KD4" s="5">
-        <f>SUM(IY4,JG4,JO4,JW4,KC4)</f>
+        <f>SUM(JX4:KC4)</f>
         <v>0</v>
       </c>
       <c r="KE4" s="5">
-        <f>SUM(AL4,BT4,DF4,EP4,GA4,HK4,IV4,KD4)</f>
+        <f>SUM(IY4,JG4,JO4,JW4,KD4)</f>
+        <v>0</v>
+      </c>
+      <c r="KF4" s="5">
+        <f>SUM(AL4,BT4,DF4,EP4,GA4,HK4,IV4,KE4)</f>
         <v>4</v>
       </c>
     </row>
@@ -15545,12 +15591,16 @@
       </c>
       <c r="KE5" s="7">
         <f>SUM(KE3,KE4)</f>
+        <v>0</v>
+      </c>
+      <c r="KF5" s="7">
+        <f>SUM(KF3,KF4)</f>
         <v>20</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:KE1"/>
+    <mergeCell ref="B1:KF1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15563,7 +15613,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:KE5"/>
+  <dimension ref="A1:KF5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -15854,9 +15904,10 @@
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="286" max="286"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="287" max="287"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="288" max="288"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="289" max="289"/>
-    <col collapsed="1" width="13" customWidth="1" min="290" max="290"/>
-    <col width="14" customWidth="1" min="291" max="291"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="289" max="289"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="290" max="290"/>
+    <col collapsed="1" width="13" customWidth="1" min="291" max="291"/>
+    <col width="14" customWidth="1" min="292" max="292"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16159,6 +16210,7 @@
       <c r="KC1" s="12" t="n"/>
       <c r="KD1" s="12" t="n"/>
       <c r="KE1" s="12" t="n"/>
+      <c r="KF1" s="12" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n"/>
@@ -17599,15 +17651,20 @@
       </c>
       <c r="KC2" s="12" t="inlineStr">
         <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="KD2" s="12" t="inlineStr">
+        <is>
           <t>W5 Aug</t>
         </is>
       </c>
-      <c r="KD2" s="12" t="inlineStr">
+      <c r="KE2" s="12" t="inlineStr">
         <is>
           <t>Aug Total</t>
         </is>
       </c>
-      <c r="KE2" s="12" t="inlineStr">
+      <c r="KF2" s="12" t="inlineStr">
         <is>
           <t>YTD Total</t>
         </is>
@@ -18527,16 +18584,19 @@
       <c r="KB3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="KC3" s="5">
-        <f>SUM(JX3:KB3)</f>
+      <c r="KC3" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KD3" s="5">
+        <f>SUM(JX3:KC3)</f>
         <v>6</v>
       </c>
-      <c r="KD3" s="5">
-        <f>SUM(IY3,JG3,JO3,JW3,KC3)</f>
+      <c r="KE3" s="5">
+        <f>SUM(IY3,JG3,JO3,JW3,KD3)</f>
         <v>15</v>
       </c>
-      <c r="KE3" s="5">
-        <f>SUM(AL3,BT3,DF3,EP3,GA3,HK3,IV3,KD3)</f>
+      <c r="KF3" s="5">
+        <f>SUM(AL3,BT3,DF3,EP3,GA3,HK3,IV3,KE3)</f>
         <v>150</v>
       </c>
     </row>
@@ -19454,16 +19514,19 @@
       <c r="KB4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="KC4" s="5">
-        <f>SUM(JX4:KB4)</f>
+      <c r="KC4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KD4" s="5">
+        <f>SUM(JX4:KC4)</f>
         <v>4</v>
       </c>
-      <c r="KD4" s="5">
-        <f>SUM(IY4,JG4,JO4,JW4,KC4)</f>
+      <c r="KE4" s="5">
+        <f>SUM(IY4,JG4,JO4,JW4,KD4)</f>
         <v>8</v>
       </c>
-      <c r="KE4" s="5">
-        <f>SUM(AL4,BT4,DF4,EP4,GA4,HK4,IV4,KD4)</f>
+      <c r="KF4" s="5">
+        <f>SUM(AL4,BT4,DF4,EP4,GA4,HK4,IV4,KE4)</f>
         <v>92</v>
       </c>
     </row>
@@ -20623,20 +20686,24 @@
       </c>
       <c r="KC5" s="7">
         <f>SUM(KC3,KC4)</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="KD5" s="7">
         <f>SUM(KD3,KD4)</f>
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="KE5" s="7">
         <f>SUM(KE3,KE4)</f>
+        <v>23</v>
+      </c>
+      <c r="KF5" s="7">
+        <f>SUM(KF3,KF4)</f>
         <v>242</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:KE1"/>
+    <mergeCell ref="B1:KF1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -20649,7 +20716,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:KE5"/>
+  <dimension ref="A1:KF5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -20940,9 +21007,10 @@
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="286" max="286"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="287" max="287"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="288" max="288"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="289" max="289"/>
-    <col collapsed="1" width="13" customWidth="1" min="290" max="290"/>
-    <col width="14" customWidth="1" min="291" max="291"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="289" max="289"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="290" max="290"/>
+    <col collapsed="1" width="13" customWidth="1" min="291" max="291"/>
+    <col width="14" customWidth="1" min="292" max="292"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -21245,6 +21313,7 @@
       <c r="KC1" s="13" t="n"/>
       <c r="KD1" s="13" t="n"/>
       <c r="KE1" s="13" t="n"/>
+      <c r="KF1" s="13" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n"/>
@@ -22685,15 +22754,20 @@
       </c>
       <c r="KC2" s="13" t="inlineStr">
         <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="KD2" s="13" t="inlineStr">
+        <is>
           <t>W5 Aug</t>
         </is>
       </c>
-      <c r="KD2" s="13" t="inlineStr">
+      <c r="KE2" s="13" t="inlineStr">
         <is>
           <t>Aug Total</t>
         </is>
       </c>
-      <c r="KE2" s="13" t="inlineStr">
+      <c r="KF2" s="13" t="inlineStr">
         <is>
           <t>YTD Total</t>
         </is>
@@ -23613,16 +23687,19 @@
       <c r="KB3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="KC3" s="5">
-        <f>SUM(JX3:KB3)</f>
+      <c r="KC3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="KD3" s="5">
-        <f>SUM(IY3,JG3,JO3,JW3,KC3)</f>
+        <f>SUM(JX3:KC3)</f>
         <v>0</v>
       </c>
       <c r="KE3" s="5">
-        <f>SUM(AL3,BT3,DF3,EP3,GA3,HK3,IV3,KD3)</f>
+        <f>SUM(IY3,JG3,JO3,JW3,KD3)</f>
+        <v>0</v>
+      </c>
+      <c r="KF3" s="5">
+        <f>SUM(AL3,BT3,DF3,EP3,GA3,HK3,IV3,KE3)</f>
         <v>0</v>
       </c>
     </row>
@@ -24540,16 +24617,19 @@
       <c r="KB4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="KC4" s="5">
-        <f>SUM(JX4:KB4)</f>
+      <c r="KC4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="KD4" s="5">
+        <f>SUM(JX4:KC4)</f>
         <v>4</v>
       </c>
-      <c r="KD4" s="5">
-        <f>SUM(IY4,JG4,JO4,JW4,KC4)</f>
+      <c r="KE4" s="5">
+        <f>SUM(IY4,JG4,JO4,JW4,KD4)</f>
         <v>4</v>
       </c>
-      <c r="KE4" s="5">
-        <f>SUM(AL4,BT4,DF4,EP4,GA4,HK4,IV4,KD4)</f>
+      <c r="KF4" s="5">
+        <f>SUM(AL4,BT4,DF4,EP4,GA4,HK4,IV4,KE4)</f>
         <v>4</v>
       </c>
     </row>
@@ -25709,7 +25789,7 @@
       </c>
       <c r="KC5" s="7">
         <f>SUM(KC3,KC4)</f>
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="KD5" s="7">
         <f>SUM(KD3,KD4)</f>
@@ -25719,10 +25799,14 @@
         <f>SUM(KE3,KE4)</f>
         <v>4</v>
       </c>
+      <c r="KF5" s="7">
+        <f>SUM(KF3,KF4)</f>
+        <v>4</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:KE1"/>
+    <mergeCell ref="B1:KF1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25735,7 +25819,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:KM5"/>
+  <dimension ref="A1:KN5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -26033,10 +26117,11 @@
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="293" max="293"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="294" max="294"/>
     <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="295" max="295"/>
-    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="296" max="296"/>
-    <col collapsed="1" width="13" customWidth="1" min="297" max="297"/>
-    <col width="12" customWidth="1" min="298" max="298"/>
-    <col width="14" customWidth="1" min="299" max="299"/>
+    <col hidden="1" outlineLevel="2" width="11" customWidth="1" min="296" max="296"/>
+    <col hidden="1" outlineLevel="1" collapsed="1" width="13" customWidth="1" min="297" max="297"/>
+    <col collapsed="1" width="13" customWidth="1" min="298" max="298"/>
+    <col width="12" customWidth="1" min="299" max="299"/>
+    <col width="14" customWidth="1" min="300" max="300"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -26347,6 +26432,7 @@
       <c r="KK1" s="14" t="n"/>
       <c r="KL1" s="14" t="n"/>
       <c r="KM1" s="14" t="n"/>
+      <c r="KN1" s="14" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n"/>
@@ -27822,20 +27908,25 @@
       </c>
       <c r="KJ2" s="14" t="inlineStr">
         <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="KK2" s="14" t="inlineStr">
+        <is>
           <t>W5 Aug</t>
         </is>
       </c>
-      <c r="KK2" s="14" t="inlineStr">
+      <c r="KL2" s="14" t="inlineStr">
         <is>
           <t>Aug Total</t>
         </is>
       </c>
-      <c r="KL2" s="14" t="inlineStr">
+      <c r="KM2" s="14" t="inlineStr">
         <is>
           <t>% of Target</t>
         </is>
       </c>
-      <c r="KM2" s="14" t="inlineStr">
+      <c r="KN2" s="14" t="inlineStr">
         <is>
           <t>YTD Total</t>
         </is>
@@ -28783,20 +28874,23 @@
       <c r="KI3" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="KJ3" s="5">
-        <f>SUM(KE3:KI3)</f>
+      <c r="KJ3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="KK3" s="5">
-        <f>SUM(JF3,JN3,JV3,KD3,KJ3)</f>
+        <f>SUM(KE3:KJ3)</f>
+        <v>0</v>
+      </c>
+      <c r="KL3" s="5">
+        <f>SUM(JF3,JN3,JV3,KD3,KK3)</f>
         <v>7</v>
       </c>
-      <c r="KL3" s="15">
-        <f>KK3/440</f>
+      <c r="KM3" s="15">
+        <f>KL3/440</f>
         <v>0.015909090909090907</v>
       </c>
-      <c r="KM3" s="5">
-        <f>SUM(AL3,BU3,DH3,ES3,GE3,HP3,JB3,KK3)</f>
+      <c r="KN3" s="5">
+        <f>SUM(AL3,BU3,DH3,ES3,GE3,HP3,JB3,KL3)</f>
         <v>63</v>
       </c>
     </row>
@@ -29742,20 +29836,23 @@
       <c r="KI4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="KJ4" s="5">
-        <f>SUM(KE4:KI4)</f>
-        <v>1</v>
+      <c r="KJ4" s="5" t="n">
+        <v>0</v>
       </c>
       <c r="KK4" s="5">
-        <f>SUM(JF4,JN4,JV4,KD4,KJ4)</f>
+        <f>SUM(KE4:KJ4)</f>
+        <v>1</v>
+      </c>
+      <c r="KL4" s="5">
+        <f>SUM(JF4,JN4,JV4,KD4,KK4)</f>
         <v>16</v>
       </c>
-      <c r="KL4" s="15">
-        <f>KK4/440</f>
+      <c r="KM4" s="15">
+        <f>KL4/440</f>
         <v>0.03636363636363636</v>
       </c>
-      <c r="KM4" s="5">
-        <f>SUM(AL4,BU4,DH4,ES4,GE4,HP4,JB4,KK4)</f>
+      <c r="KN4" s="5">
+        <f>SUM(AL4,BU4,DH4,ES4,GE4,HP4,JB4,KL4)</f>
         <v>77</v>
       </c>
     </row>
@@ -30943,24 +31040,28 @@
       </c>
       <c r="KJ5" s="7">
         <f>SUM(KJ3,KJ4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="KK5" s="7">
         <f>SUM(KK3,KK4)</f>
+        <v>1</v>
+      </c>
+      <c r="KL5" s="7">
+        <f>SUM(KL3,KL4)</f>
         <v>23</v>
       </c>
-      <c r="KL5" s="16">
-        <f>KK5/880</f>
+      <c r="KM5" s="16">
+        <f>KL5/880</f>
         <v>0.026136363636363635</v>
       </c>
-      <c r="KM5" s="7">
-        <f>SUM(KM3,KM4)</f>
+      <c r="KN5" s="7">
+        <f>SUM(KN3,KN4)</f>
         <v>140</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:KM1"/>
+    <mergeCell ref="B1:KN1"/>
     <mergeCell ref="A1:A2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
